--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_MoraBanc Andorra.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_MoraBanc Andorra.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2169.16</v>
+        <v>2469.52</v>
       </c>
       <c r="C2" t="n">
-        <v>2179.6</v>
+        <v>2485.02</v>
       </c>
       <c r="D2" t="n">
-        <v>110.5248669480638</v>
+        <v>111.2667101270815</v>
       </c>
       <c r="E2" t="n">
-        <v>119.8385024775188</v>
+        <v>119.9587930881844</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5286931818181818</v>
+        <v>0.5351485148514852</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1620528316600059</v>
+        <v>0.1614098598976669</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2983706720977597</v>
+        <v>0.3017009847806625</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3113636363636363</v>
+        <v>0.2985148514851485</v>
       </c>
       <c r="J2" t="n">
-        <v>289</v>
+        <v>322</v>
       </c>
       <c r="K2" t="n">
-        <v>307</v>
+        <v>348</v>
       </c>
       <c r="L2" t="n">
-        <v>150</v>
+        <v>183</v>
       </c>
       <c r="M2" t="n">
-        <v>379</v>
+        <v>431</v>
       </c>
       <c r="N2" t="n">
-        <v>816</v>
+        <v>926</v>
       </c>
       <c r="O2" t="n">
-        <v>1061</v>
+        <v>1199</v>
       </c>
       <c r="P2" t="n">
-        <v>0.602840909090909</v>
+        <v>0.5935643564356435</v>
       </c>
       <c r="Q2" t="n">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="R2" t="n">
-        <v>342</v>
+        <v>380</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1943181818181818</v>
+        <v>0.1881188118811881</v>
       </c>
       <c r="T2" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="U2" t="n">
-        <v>246</v>
+        <v>282</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1397727272727273</v>
+        <v>0.1396039603960396</v>
       </c>
       <c r="W2" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="X2" t="n">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09659090909090909</v>
+        <v>0.09455445544554456</v>
       </c>
       <c r="Z2" t="n">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="AA2" t="n">
-        <v>630</v>
+        <v>726</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3579545454545455</v>
+        <v>0.3594059405940594</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7690857681432611</v>
+        <v>0.7723102585487907</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.412280701754386</v>
+        <v>0.4157894736842105</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3455284552845528</v>
+        <v>0.351063829787234</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3411764705882353</v>
+        <v>0.3455497382198953</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3698412698412699</v>
+        <v>0.3691460055096419</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.538171536286522</v>
+        <v>1.544620517097581</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.6910569105691057</v>
+        <v>0.7021276595744681</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.09125</v>
+        <v>1.092693565976009</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8210227272727273</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.04778156996587</v>
+        <v>1.032640949554896</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.685393258426966</v>
+        <v>1.663636363636364</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.137844611528822</v>
+        <v>1.154525386313466</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.411027568922306</v>
+        <v>4.459161147902869</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.548872180451128</v>
+        <v>5.613686534216336</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77.47</v>
+        <v>77.1725</v>
       </c>
       <c r="C3" t="n">
-        <v>77.84285714285716</v>
+        <v>77.656875</v>
       </c>
       <c r="D3" t="n">
-        <v>110.5248669480639</v>
+        <v>111.2667101270815</v>
       </c>
       <c r="E3" t="n">
-        <v>119.8385024775188</v>
+        <v>119.9587930881844</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5286931818181817</v>
+        <v>0.5351485148514852</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1620528316600058</v>
+        <v>0.1614098598976669</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2983706720977597</v>
+        <v>0.3017009847806625</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3113636363636363</v>
+        <v>0.2985148514851485</v>
       </c>
       <c r="J3" t="n">
-        <v>10.32142857142857</v>
+        <v>10.0625</v>
       </c>
       <c r="K3" t="n">
-        <v>10.96428571428571</v>
+        <v>10.875</v>
       </c>
       <c r="L3" t="n">
-        <v>5.357142857142857</v>
+        <v>5.71875</v>
       </c>
       <c r="M3" t="n">
-        <v>13.53571428571429</v>
+        <v>13.46875</v>
       </c>
       <c r="N3" t="n">
-        <v>29.14285714285714</v>
+        <v>28.9375</v>
       </c>
       <c r="O3" t="n">
-        <v>37.89285714285715</v>
+        <v>37.46875</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6028409090909091</v>
+        <v>0.5935643564356435</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.035714285714286</v>
+        <v>4.9375</v>
       </c>
       <c r="R3" t="n">
-        <v>12.21428571428571</v>
+        <v>11.875</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1943181818181818</v>
+        <v>0.1881188118811881</v>
       </c>
       <c r="T3" t="n">
-        <v>3.035714285714286</v>
+        <v>3.09375</v>
       </c>
       <c r="U3" t="n">
-        <v>8.785714285714286</v>
+        <v>8.8125</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1397727272727273</v>
+        <v>0.1396039603960396</v>
       </c>
       <c r="W3" t="n">
-        <v>2.071428571428572</v>
+        <v>2.0625</v>
       </c>
       <c r="X3" t="n">
-        <v>6.071428571428571</v>
+        <v>5.96875</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.09659090909090907</v>
+        <v>0.09455445544554456</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.321428571428571</v>
+        <v>8.375</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.5</v>
+        <v>22.6875</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3579545454545454</v>
+        <v>0.3594059405940594</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.769085768143261</v>
+        <v>0.7723102585487907</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.412280701754386</v>
+        <v>0.4157894736842105</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3455284552845528</v>
+        <v>0.351063829787234</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3411764705882354</v>
+        <v>0.3455497382198953</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3698412698412698</v>
+        <v>0.3691460055096419</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.538171536286522</v>
+        <v>1.544620517097581</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.6910569105691056</v>
+        <v>0.7021276595744681</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.09125</v>
+        <v>1.092693565976009</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8210227272727273</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.04778156996587</v>
+        <v>1.032640949554896</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.685393258426966</v>
+        <v>1.663636363636364</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.137844611528822</v>
+        <v>1.154525386313466</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.411027568922306</v>
+        <v>4.459161147902869</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.548872180451129</v>
+        <v>5.613686534216336</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2190.04</v>
+        <v>2500.52</v>
       </c>
       <c r="C4" t="n">
-        <v>2179.6</v>
+        <v>2485.02</v>
       </c>
       <c r="D4" t="n">
-        <v>119.8385024775188</v>
+        <v>119.9587930881844</v>
       </c>
       <c r="E4" t="n">
-        <v>110.5248669480638</v>
+        <v>111.2667101270815</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5596453519613112</v>
+        <v>0.5545963602426505</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1392383031914052</v>
+        <v>0.1353165923752042</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3376623376623377</v>
+        <v>0.3365051903114187</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2842557764642665</v>
+        <v>0.2818478768082128</v>
       </c>
       <c r="J4" t="n">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="K4" t="n">
-        <v>344</v>
+        <v>398</v>
       </c>
       <c r="L4" t="n">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="M4" t="n">
-        <v>329</v>
+        <v>367</v>
       </c>
       <c r="N4" t="n">
-        <v>871</v>
+        <v>1000</v>
       </c>
       <c r="O4" t="n">
-        <v>1151</v>
+        <v>1319</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6184846856528748</v>
+        <v>0.6154923005132991</v>
       </c>
       <c r="Q4" t="n">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="R4" t="n">
-        <v>323</v>
+        <v>374</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1735626007522837</v>
+        <v>0.1745216985534298</v>
       </c>
       <c r="T4" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="U4" t="n">
-        <v>224</v>
+        <v>259</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1203653949489522</v>
+        <v>0.1208586094260383</v>
       </c>
       <c r="W4" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="X4" t="n">
-        <v>211</v>
+        <v>240</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1133799032778076</v>
+        <v>0.1119925338310779</v>
       </c>
       <c r="Z4" t="n">
-        <v>219</v>
+        <v>254</v>
       </c>
       <c r="AA4" t="n">
-        <v>668</v>
+        <v>759</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3589468027941967</v>
+        <v>0.354176388240784</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7567332754126846</v>
+        <v>0.7581501137225171</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.5170278637770898</v>
+        <v>0.4973262032085561</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3482142857142857</v>
+        <v>0.3552123552123552</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3981042654028436</v>
+        <v>0.3708333333333333</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3278443113772455</v>
+        <v>0.3346508563899868</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.513466550825369</v>
+        <v>1.516300227445034</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.6964285714285714</v>
+        <v>0.7104247104247104</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.034129692832765</v>
+        <v>1.03003003003003</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8195488721804511</v>
+        <v>0.8123620309050773</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.017751479289941</v>
+        <v>1.023136246786632</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.790909090909091</v>
+        <v>1.763779527559055</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.545454545454545</v>
+        <v>1.572890025575448</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.286931818181818</v>
+        <v>5.48081841432225</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.832386363636363</v>
+        <v>7.053708439897698</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78.21571428571428</v>
+        <v>78.14125</v>
       </c>
       <c r="C5" t="n">
-        <v>77.84285714285716</v>
+        <v>77.656875</v>
       </c>
       <c r="D5" t="n">
-        <v>119.8385024775188</v>
+        <v>119.9587930881844</v>
       </c>
       <c r="E5" t="n">
-        <v>110.5248669480639</v>
+        <v>111.2667101270815</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5596453519613112</v>
+        <v>0.5545963602426505</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1392383031914052</v>
+        <v>0.1353165923752042</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3376623376623377</v>
+        <v>0.3365051903114187</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2842557764642665</v>
+        <v>0.2818478768082128</v>
       </c>
       <c r="J5" t="n">
-        <v>11.67857142857143</v>
+        <v>11.5</v>
       </c>
       <c r="K5" t="n">
-        <v>12.28571428571429</v>
+        <v>12.4375</v>
       </c>
       <c r="L5" t="n">
-        <v>7.035714285714286</v>
+        <v>7</v>
       </c>
       <c r="M5" t="n">
-        <v>11.75</v>
+        <v>11.46875</v>
       </c>
       <c r="N5" t="n">
-        <v>31.10714285714286</v>
+        <v>31.25</v>
       </c>
       <c r="O5" t="n">
-        <v>41.10714285714285</v>
+        <v>41.21875</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6184846856528748</v>
+        <v>0.6154923005132991</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.964285714285714</v>
+        <v>5.8125</v>
       </c>
       <c r="R5" t="n">
-        <v>11.53571428571429</v>
+        <v>11.6875</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1735626007522837</v>
+        <v>0.1745216985534298</v>
       </c>
       <c r="T5" t="n">
-        <v>2.785714285714286</v>
+        <v>2.875</v>
       </c>
       <c r="U5" t="n">
-        <v>8</v>
+        <v>8.09375</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1203653949489522</v>
+        <v>0.1208586094260383</v>
       </c>
       <c r="W5" t="n">
-        <v>3</v>
+        <v>2.78125</v>
       </c>
       <c r="X5" t="n">
-        <v>7.535714285714286</v>
+        <v>7.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1133799032778076</v>
+        <v>0.1119925338310779</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.821428571428571</v>
+        <v>7.9375</v>
       </c>
       <c r="AA5" t="n">
-        <v>23.85714285714286</v>
+        <v>23.71875</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3589468027941967</v>
+        <v>0.354176388240784</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7567332754126846</v>
+        <v>0.7581501137225171</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.5170278637770898</v>
+        <v>0.4973262032085561</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3482142857142857</v>
+        <v>0.3552123552123552</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3981042654028436</v>
+        <v>0.3708333333333333</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3278443113772455</v>
+        <v>0.3346508563899868</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.513466550825369</v>
+        <v>1.516300227445034</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.6964285714285714</v>
+        <v>0.7104247104247104</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.034129692832765</v>
+        <v>1.03003003003003</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8195488721804511</v>
+        <v>0.8123620309050773</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.017751479289941</v>
+        <v>1.023136246786632</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.790909090909091</v>
+        <v>1.763779527559055</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.545454545454545</v>
+        <v>1.572890025575448</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.286931818181817</v>
+        <v>5.48081841432225</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.832386363636363</v>
+        <v>7.053708439897698</v>
       </c>
     </row>
     <row r="7">
@@ -1419,100 +1419,100 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>338</v>
+        <v>391</v>
       </c>
       <c r="D8" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="E8" t="n">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="F8" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
+        <v>164</v>
+      </c>
+      <c r="H8" t="n">
+        <v>107</v>
+      </c>
+      <c r="I8" t="n">
+        <v>129</v>
+      </c>
+      <c r="J8" t="n">
+        <v>169</v>
+      </c>
+      <c r="K8" t="n">
+        <v>60</v>
+      </c>
+      <c r="L8" t="n">
+        <v>11</v>
+      </c>
+      <c r="M8" t="n">
+        <v>37</v>
+      </c>
+      <c r="N8" t="n">
+        <v>17</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>95</v>
+      </c>
+      <c r="R8" t="n">
+        <v>60</v>
+      </c>
+      <c r="S8" t="n">
         <v>139</v>
       </c>
-      <c r="H8" t="n">
-        <v>99</v>
-      </c>
-      <c r="I8" t="n">
-        <v>120</v>
-      </c>
-      <c r="J8" t="n">
-        <v>148</v>
-      </c>
-      <c r="K8" t="n">
-        <v>49</v>
-      </c>
-      <c r="L8" t="n">
-        <v>10</v>
-      </c>
-      <c r="M8" t="n">
-        <v>33</v>
-      </c>
-      <c r="N8" t="n">
-        <v>16</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>82</v>
-      </c>
-      <c r="R8" t="n">
-        <v>53</v>
-      </c>
-      <c r="S8" t="n">
-        <v>119</v>
-      </c>
       <c r="T8" t="n">
-        <v>379</v>
+        <v>444</v>
       </c>
       <c r="U8" t="n">
         <v>51</v>
       </c>
       <c r="V8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="W8" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="X8" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="Y8" t="n">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="Z8" t="n">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.731</v>
+        <v>0.741</v>
       </c>
       <c r="AB8" t="n">
         <v>19</v>
       </c>
       <c r="AC8" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.328</v>
+        <v>0.311</v>
       </c>
       <c r="AE8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF8" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.278</v>
+        <v>0.261</v>
       </c>
       <c r="AH8" t="n">
         <v>1</v>
@@ -1524,51 +1524,51 @@
         <v>0.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="AL8" t="n">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.296</v>
+        <v>0.306</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>677:08</t>
+          <t>776:08</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>411.8</v>
+        <v>471.76</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.431</v>
+        <v>0.444</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.512</v>
+        <v>0.519</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.821</v>
+        <v>0.829</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.199</v>
+        <v>0.201</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.357</v>
+        <v>0.334</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.805</v>
+        <v>1.779</v>
       </c>
       <c r="AV8" t="n">
         <v>0.282</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.082</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.216</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="9">
@@ -1724,10 +1724,10 @@
         <v>0.105</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.161</v>
+        <v>0.159</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="10">
@@ -1883,10 +1883,10 @@
         <v>0.008</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.106</v>
+        <v>0.105</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.024</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="11">
@@ -1896,156 +1896,156 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>254</v>
+        <v>280</v>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E11" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="F11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G11" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H11" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="I11" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="J11" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K11" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L11" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Q11" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="R11" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S11" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="T11" t="n">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="U11" t="n">
         <v>38</v>
       </c>
       <c r="V11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="W11" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="X11" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Y11" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="Z11" t="n">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.795</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AB11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC11" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AD11" t="n">
         <v>0.333</v>
       </c>
       <c r="AE11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF11" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.323</v>
+        <v>0.324</v>
       </c>
       <c r="AH11" t="n">
         <v>15</v>
       </c>
       <c r="AI11" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.441</v>
+        <v>0.429</v>
       </c>
       <c r="AK11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AL11" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.397</v>
+        <v>0.372</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>602:11</t>
+          <t>678:29</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>243.28</v>
+        <v>274.36</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.524</v>
+        <v>0.509</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.582</v>
+        <v>0.571</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.044</v>
+        <v>1.021</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.103</v>
+        <v>0.106</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.283</v>
+        <v>0.284</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.32</v>
+        <v>1.276</v>
       </c>
       <c r="AV11" t="n">
         <v>0.187</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.033</v>
+        <v>0.036</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.074</v>
+        <v>0.075</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.047</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="12">
@@ -2055,67 +2055,67 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G12" t="n">
+        <v>25</v>
+      </c>
+      <c r="H12" t="n">
+        <v>31</v>
+      </c>
+      <c r="I12" t="n">
+        <v>42</v>
+      </c>
+      <c r="J12" t="n">
+        <v>85</v>
+      </c>
+      <c r="K12" t="n">
+        <v>53</v>
+      </c>
+      <c r="L12" t="n">
+        <v>17</v>
+      </c>
+      <c r="M12" t="n">
         <v>14</v>
       </c>
-      <c r="H12" t="n">
-        <v>29</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="N12" t="n">
+        <v>6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>42</v>
+      </c>
+      <c r="R12" t="n">
+        <v>45</v>
+      </c>
+      <c r="S12" t="n">
         <v>38</v>
       </c>
-      <c r="J12" t="n">
-        <v>67</v>
-      </c>
-      <c r="K12" t="n">
-        <v>41</v>
-      </c>
-      <c r="L12" t="n">
-        <v>15</v>
-      </c>
-      <c r="M12" t="n">
-        <v>10</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>37</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>37</v>
-      </c>
-      <c r="R12" t="n">
-        <v>39</v>
-      </c>
-      <c r="S12" t="n">
-        <v>34</v>
-      </c>
       <c r="T12" t="n">
-        <v>169</v>
+        <v>210</v>
       </c>
       <c r="U12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="V12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="W12" t="n">
         <v>8</v>
@@ -2124,87 +2124,87 @@
         <v>6</v>
       </c>
       <c r="Y12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Z12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.769</v>
+        <v>0.737</v>
       </c>
       <c r="AB12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AC12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.545</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AE12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.556</v>
+        <v>0.538</v>
       </c>
       <c r="AH12" t="n">
         <v>1</v>
       </c>
       <c r="AI12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AL12" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.615</v>
+        <v>0.522</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>327:54</t>
+          <t>408:24</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>101.72</v>
+        <v>129.48</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.74</v>
+        <v>0.674</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.773</v>
+        <v>0.709</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.983</v>
+        <v>0.958</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.364</v>
+        <v>0.324</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.604</v>
+        <v>0.449</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.811</v>
+        <v>2.024</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.144</v>
+        <v>0.147</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.053</v>
+        <v>0.048</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.142</v>
+        <v>0.146</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.089</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="13">
@@ -2363,7 +2363,7 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="14">
@@ -2373,156 +2373,156 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" t="n">
+        <v>163</v>
+      </c>
+      <c r="D14" t="n">
+        <v>40</v>
+      </c>
+      <c r="E14" t="n">
+        <v>77</v>
+      </c>
+      <c r="F14" t="n">
+        <v>18</v>
+      </c>
+      <c r="G14" t="n">
+        <v>45</v>
+      </c>
+      <c r="H14" t="n">
+        <v>29</v>
+      </c>
+      <c r="I14" t="n">
+        <v>40</v>
+      </c>
+      <c r="J14" t="n">
+        <v>50</v>
+      </c>
+      <c r="K14" t="n">
+        <v>36</v>
+      </c>
+      <c r="L14" t="n">
+        <v>12</v>
+      </c>
+      <c r="M14" t="n">
+        <v>7</v>
+      </c>
+      <c r="N14" t="n">
+        <v>11</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>32</v>
+      </c>
+      <c r="R14" t="n">
+        <v>31</v>
+      </c>
+      <c r="S14" t="n">
+        <v>45</v>
+      </c>
+      <c r="T14" t="n">
+        <v>186</v>
+      </c>
+      <c r="U14" t="n">
+        <v>21</v>
+      </c>
+      <c r="V14" t="n">
+        <v>23</v>
+      </c>
+      <c r="W14" t="n">
+        <v>18</v>
+      </c>
+      <c r="X14" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>35</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="AE14" t="n">
         <v>8</v>
       </c>
-      <c r="C14" t="n">
-        <v>113</v>
-      </c>
-      <c r="D14" t="n">
-        <v>28</v>
-      </c>
-      <c r="E14" t="n">
-        <v>55</v>
-      </c>
-      <c r="F14" t="n">
-        <v>12</v>
-      </c>
-      <c r="G14" t="n">
-        <v>30</v>
-      </c>
-      <c r="H14" t="n">
-        <v>21</v>
-      </c>
-      <c r="I14" t="n">
-        <v>31</v>
-      </c>
-      <c r="J14" t="n">
-        <v>42</v>
-      </c>
-      <c r="K14" t="n">
-        <v>29</v>
-      </c>
-      <c r="L14" t="n">
-        <v>9</v>
-      </c>
-      <c r="M14" t="n">
-        <v>4</v>
-      </c>
-      <c r="N14" t="n">
-        <v>7</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>25</v>
-      </c>
-      <c r="R14" t="n">
-        <v>25</v>
-      </c>
-      <c r="S14" t="n">
-        <v>33</v>
-      </c>
-      <c r="T14" t="n">
-        <v>132</v>
-      </c>
-      <c r="U14" t="n">
-        <v>16</v>
-      </c>
-      <c r="V14" t="n">
-        <v>16</v>
-      </c>
-      <c r="W14" t="n">
-        <v>15</v>
-      </c>
-      <c r="X14" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>31</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.646</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>6</v>
-      </c>
       <c r="AF14" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
       <c r="AH14" t="n">
         <v>1</v>
       </c>
       <c r="AI14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AK14" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AL14" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.44</v>
+        <v>0.436</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>218:28</t>
+          <t>298:17</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>123.64</v>
+        <v>171.6</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.541</v>
+        <v>0.549</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.573</v>
+        <v>0.584</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.914</v>
+        <v>0.95</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.202</v>
+        <v>0.186</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.247</v>
+        <v>0.238</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.68</v>
+        <v>1.562</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.262</v>
+        <v>0.266</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.151</v>
+        <v>0.136</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.056</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="15">
@@ -2532,91 +2532,91 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>26</v>
+      </c>
+      <c r="C15" t="n">
+        <v>222</v>
+      </c>
+      <c r="D15" t="n">
+        <v>45</v>
+      </c>
+      <c r="E15" t="n">
+        <v>69</v>
+      </c>
+      <c r="F15" t="n">
+        <v>32</v>
+      </c>
+      <c r="G15" t="n">
+        <v>105</v>
+      </c>
+      <c r="H15" t="n">
+        <v>36</v>
+      </c>
+      <c r="I15" t="n">
+        <v>44</v>
+      </c>
+      <c r="J15" t="n">
+        <v>28</v>
+      </c>
+      <c r="K15" t="n">
+        <v>72</v>
+      </c>
+      <c r="L15" t="n">
+        <v>19</v>
+      </c>
+      <c r="M15" t="n">
         <v>22</v>
       </c>
-      <c r="C15" t="n">
-        <v>195</v>
-      </c>
-      <c r="D15" t="n">
-        <v>40</v>
-      </c>
-      <c r="E15" t="n">
-        <v>61</v>
-      </c>
-      <c r="F15" t="n">
-        <v>28</v>
-      </c>
-      <c r="G15" t="n">
-        <v>94</v>
-      </c>
-      <c r="H15" t="n">
+      <c r="N15" t="n">
+        <v>13</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>23</v>
+      </c>
+      <c r="R15" t="n">
+        <v>64</v>
+      </c>
+      <c r="S15" t="n">
+        <v>32</v>
+      </c>
+      <c r="T15" t="n">
+        <v>216</v>
+      </c>
+      <c r="U15" t="n">
+        <v>38</v>
+      </c>
+      <c r="V15" t="n">
         <v>31</v>
       </c>
-      <c r="I15" t="n">
-        <v>38</v>
-      </c>
-      <c r="J15" t="n">
+      <c r="W15" t="n">
+        <v>16</v>
+      </c>
+      <c r="X15" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC15" t="n">
         <v>23</v>
       </c>
-      <c r="K15" t="n">
-        <v>61</v>
-      </c>
-      <c r="L15" t="n">
-        <v>18</v>
-      </c>
-      <c r="M15" t="n">
-        <v>19</v>
-      </c>
-      <c r="N15" t="n">
-        <v>12</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>20</v>
-      </c>
-      <c r="R15" t="n">
-        <v>53</v>
-      </c>
-      <c r="S15" t="n">
-        <v>29</v>
-      </c>
-      <c r="T15" t="n">
-        <v>190</v>
-      </c>
-      <c r="U15" t="n">
-        <v>28</v>
-      </c>
-      <c r="V15" t="n">
-        <v>29</v>
-      </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>49</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>63</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>21</v>
-      </c>
       <c r="AD15" t="n">
-        <v>0.524</v>
+        <v>0.522</v>
       </c>
       <c r="AE15" t="n">
         <v>11</v>
@@ -2628,60 +2628,60 @@
         <v>0.733</v>
       </c>
       <c r="AH15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI15" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.273</v>
+        <v>0.289</v>
       </c>
       <c r="AK15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.311</v>
+        <v>0.313</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>490:15</t>
+          <t>562:46</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>191.72</v>
+        <v>216.36</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.529</v>
+        <v>0.534</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.574</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.017</v>
+        <v>1.026</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.104</v>
+        <v>0.106</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.2</v>
+        <v>0.207</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.15</v>
+        <v>1.217</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.181</v>
+        <v>0.178</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.043</v>
+        <v>0.039</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.142</v>
+        <v>0.144</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.032</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="16">
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -2706,25 +2706,25 @@
         <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I16" t="n">
+        <v>22</v>
+      </c>
+      <c r="J16" t="n">
+        <v>17</v>
+      </c>
+      <c r="K16" t="n">
+        <v>50</v>
+      </c>
+      <c r="L16" t="n">
+        <v>15</v>
+      </c>
+      <c r="M16" t="n">
         <v>20</v>
-      </c>
-      <c r="J16" t="n">
-        <v>16</v>
-      </c>
-      <c r="K16" t="n">
-        <v>48</v>
-      </c>
-      <c r="L16" t="n">
-        <v>14</v>
-      </c>
-      <c r="M16" t="n">
-        <v>19</v>
       </c>
       <c r="N16" t="n">
         <v>3</v>
@@ -2733,19 +2733,19 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R16" t="n">
         <v>43</v>
       </c>
       <c r="S16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T16" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="U16" t="n">
         <v>8</v>
@@ -2760,13 +2760,13 @@
         <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Z16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.6</v>
+        <v>0.625</v>
       </c>
       <c r="AB16" t="n">
         <v>4</v>
@@ -2790,57 +2790,57 @@
         <v>5</v>
       </c>
       <c r="AI16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.238</v>
+        <v>0.227</v>
       </c>
       <c r="AK16" t="n">
         <v>3</v>
       </c>
       <c r="AL16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.3</v>
+        <v>0.273</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>367:50</t>
+          <t>380:28</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>78.8</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.333</v>
+        <v>0.323</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.407</v>
+        <v>0.405</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.711</v>
+        <v>0.701</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.127</v>
+        <v>0.133</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.267</v>
+        <v>0.29</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.6</v>
+        <v>1.545</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.099</v>
+        <v>0.101</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.044</v>
+        <v>0.046</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.149</v>
+        <v>0.148</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.021</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="17">
@@ -2850,16 +2850,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E17" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="F17" t="n">
         <v>3</v>
@@ -2868,50 +2868,50 @@
         <v>10</v>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I17" t="n">
+        <v>20</v>
+      </c>
+      <c r="J17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K17" t="n">
+        <v>29</v>
+      </c>
+      <c r="L17" t="n">
+        <v>27</v>
+      </c>
+      <c r="M17" t="n">
+        <v>7</v>
+      </c>
+      <c r="N17" t="n">
         <v>14</v>
       </c>
-      <c r="J17" t="n">
-        <v>9</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>23</v>
+      </c>
+      <c r="R17" t="n">
+        <v>44</v>
+      </c>
+      <c r="S17" t="n">
+        <v>23</v>
+      </c>
+      <c r="T17" t="n">
+        <v>103</v>
+      </c>
+      <c r="U17" t="n">
+        <v>10</v>
+      </c>
+      <c r="V17" t="n">
         <v>22</v>
       </c>
-      <c r="L17" t="n">
-        <v>19</v>
-      </c>
-      <c r="M17" t="n">
-        <v>5</v>
-      </c>
-      <c r="N17" t="n">
-        <v>11</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>20</v>
-      </c>
-      <c r="R17" t="n">
-        <v>36</v>
-      </c>
-      <c r="S17" t="n">
-        <v>20</v>
-      </c>
-      <c r="T17" t="n">
-        <v>67</v>
-      </c>
-      <c r="U17" t="n">
-        <v>8</v>
-      </c>
-      <c r="V17" t="n">
-        <v>14</v>
-      </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
@@ -2919,31 +2919,31 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="Z17" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.762</v>
+        <v>0.797</v>
       </c>
       <c r="AB17" t="n">
         <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
       </c>
       <c r="AF17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.1</v>
+        <v>0.091</v>
       </c>
       <c r="AH17" t="n">
         <v>2</v>
@@ -2965,41 +2965,41 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>242:34</t>
+          <t>297:30</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>81.16</v>
+        <v>99.8</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.555</v>
+        <v>0.596</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.612</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.85</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.246</v>
+        <v>0.23</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.145</v>
+        <v>0.191</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.45</v>
+        <v>0.522</v>
       </c>
       <c r="AV17" t="n">
         <v>0.155</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.091</v>
+        <v>0.106</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.103</v>
+        <v>0.11</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.012</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="18">
@@ -3152,13 +3152,13 @@
         <v>0.187</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.067</v>
+        <v>0.068</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -3168,67 +3168,67 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C19" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="D19" t="n">
+        <v>31</v>
+      </c>
+      <c r="E19" t="n">
+        <v>74</v>
+      </c>
+      <c r="F19" t="n">
+        <v>31</v>
+      </c>
+      <c r="G19" t="n">
+        <v>103</v>
+      </c>
+      <c r="H19" t="n">
+        <v>41</v>
+      </c>
+      <c r="I19" t="n">
+        <v>46</v>
+      </c>
+      <c r="J19" t="n">
+        <v>17</v>
+      </c>
+      <c r="K19" t="n">
+        <v>61</v>
+      </c>
+      <c r="L19" t="n">
         <v>29</v>
-      </c>
-      <c r="E19" t="n">
-        <v>70</v>
-      </c>
-      <c r="F19" t="n">
-        <v>29</v>
-      </c>
-      <c r="G19" t="n">
-        <v>91</v>
-      </c>
-      <c r="H19" t="n">
-        <v>39</v>
-      </c>
-      <c r="I19" t="n">
-        <v>44</v>
-      </c>
-      <c r="J19" t="n">
-        <v>16</v>
-      </c>
-      <c r="K19" t="n">
-        <v>56</v>
-      </c>
-      <c r="L19" t="n">
-        <v>27</v>
       </c>
       <c r="M19" t="n">
         <v>18</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="S19" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="T19" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="U19" t="n">
         <v>24</v>
       </c>
       <c r="V19" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
@@ -3237,22 +3237,22 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="Z19" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.803</v>
+        <v>0.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.478</v>
+        <v>0.48</v>
       </c>
       <c r="AE19" t="n">
         <v>8</v>
@@ -3264,60 +3264,60 @@
         <v>0.267</v>
       </c>
       <c r="AH19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI19" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.4</v>
+        <v>0.368</v>
       </c>
       <c r="AK19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.303</v>
+        <v>0.286</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>466:11</t>
+          <t>527:29</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>198.36</v>
+        <v>216.24</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.45</v>
+        <v>0.438</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.51</v>
+        <v>0.497</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.928</v>
+        <v>0.906</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.091</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.242</v>
+        <v>0.232</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.889</v>
+        <v>0.895</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.197</v>
+        <v>0.19</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.067</v>
+        <v>0.064</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.137</v>
+        <v>0.13</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="20">
@@ -3327,40 +3327,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C20" t="n">
-        <v>302</v>
+        <v>341</v>
       </c>
       <c r="D20" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E20" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F20" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G20" t="n">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="H20" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I20" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J20" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K20" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="L20" t="n">
+        <v>17</v>
+      </c>
+      <c r="M20" t="n">
         <v>14</v>
-      </c>
-      <c r="M20" t="n">
-        <v>13</v>
       </c>
       <c r="N20" t="n">
         <v>10</v>
@@ -3369,114 +3369,114 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q20" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="R20" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="S20" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="T20" t="n">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="U20" t="n">
+        <v>19</v>
+      </c>
+      <c r="V20" t="n">
+        <v>30</v>
+      </c>
+      <c r="W20" t="n">
         <v>15</v>
       </c>
-      <c r="V20" t="n">
-        <v>27</v>
-      </c>
-      <c r="W20" t="n">
-        <v>12</v>
-      </c>
       <c r="X20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y20" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="Z20" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.847</v>
+        <v>0.844</v>
       </c>
       <c r="AB20" t="n">
         <v>12</v>
       </c>
       <c r="AC20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="AE20" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AF20" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.283</v>
+        <v>0.304</v>
       </c>
       <c r="AH20" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AI20" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.579</v>
+        <v>0.6</v>
       </c>
       <c r="AK20" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="AL20" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.432</v>
+        <v>0.434</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>577:17</t>
+          <t>643:24</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>276.16</v>
+        <v>309.36</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.547</v>
+        <v>0.555</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.596</v>
+        <v>0.602</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.094</v>
+        <v>1.102</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.083</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.249</v>
+        <v>0.237</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.522</v>
+        <v>1.385</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.221</v>
+        <v>0.223</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.028</v>
+        <v>0.031</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.083</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.051</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="21">
@@ -3486,16 +3486,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C21" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E21" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -3504,25 +3504,25 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
         <v>8</v>
       </c>
       <c r="K21" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3534,43 +3534,43 @@
         <v>7</v>
       </c>
       <c r="R21" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="S21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T21" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="U21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V21" t="n">
         <v>17</v>
       </c>
       <c r="W21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z21" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.75</v>
+        <v>0.762</v>
       </c>
       <c r="AB21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.467</v>
+        <v>0.5</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3601,41 +3601,41 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>216:20</t>
+          <t>229:10</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>50.68</v>
+        <v>52.56</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.647</v>
+        <v>0.657</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.675</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.164</v>
+        <v>1.199</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.138</v>
+        <v>0.133</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.441</v>
+        <v>0.486</v>
       </c>
       <c r="AU21" t="n">
         <v>1.143</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.108</v>
+        <v>0.106</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.123</v>
+        <v>0.122</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.184</v>
+        <v>0.182</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -3645,22 +3645,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C22" t="n">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="D22" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E22" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F22" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G22" t="n">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="H22" t="n">
         <v>15</v>
@@ -3669,43 +3669,43 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K22" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="L22" t="n">
+        <v>16</v>
+      </c>
+      <c r="M22" t="n">
+        <v>17</v>
+      </c>
+      <c r="N22" t="n">
         <v>15</v>
       </c>
-      <c r="M22" t="n">
-        <v>13</v>
-      </c>
-      <c r="N22" t="n">
-        <v>10</v>
-      </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="S22" t="n">
         <v>21</v>
       </c>
       <c r="T22" t="n">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="U22" t="n">
         <v>24</v>
       </c>
       <c r="V22" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W22" t="n">
         <v>20</v>
@@ -3717,84 +3717,84 @@
         <v>30</v>
       </c>
       <c r="Z22" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.769</v>
       </c>
       <c r="AB22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.417</v>
+        <v>0.429</v>
       </c>
       <c r="AE22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.571</v>
+        <v>0.6</v>
       </c>
       <c r="AH22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI22" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.207</v>
+        <v>0.226</v>
       </c>
       <c r="AK22" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AL22" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.475</v>
+        <v>0.484</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>536:26</t>
+          <t>630:35</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>178.24</v>
+        <v>200.24</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.623</v>
+        <v>0.632</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.633</v>
+        <v>0.641</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.139</v>
+        <v>1.154</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.101</v>
+        <v>0.1</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.099</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.278</v>
+        <v>0.35</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.154</v>
+        <v>0.147</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.106</v>
+        <v>0.116</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="23">
@@ -3804,16 +3804,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C23" t="n">
-        <v>315</v>
+        <v>381</v>
       </c>
       <c r="D23" t="n">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="E23" t="n">
-        <v>160</v>
+        <v>196</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -3822,82 +3822,82 @@
         <v>4</v>
       </c>
       <c r="H23" t="n">
+        <v>112</v>
+      </c>
+      <c r="I23" t="n">
+        <v>138</v>
+      </c>
+      <c r="J23" t="n">
+        <v>23</v>
+      </c>
+      <c r="K23" t="n">
+        <v>90</v>
+      </c>
+      <c r="L23" t="n">
+        <v>54</v>
+      </c>
+      <c r="M23" t="n">
+        <v>9</v>
+      </c>
+      <c r="N23" t="n">
+        <v>27</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>60</v>
+      </c>
+      <c r="R23" t="n">
         <v>102</v>
       </c>
-      <c r="I23" t="n">
-        <v>121</v>
-      </c>
-      <c r="J23" t="n">
-        <v>18</v>
-      </c>
-      <c r="K23" t="n">
-        <v>78</v>
-      </c>
-      <c r="L23" t="n">
-        <v>44</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="S23" t="n">
+        <v>145</v>
+      </c>
+      <c r="T23" t="n">
+        <v>475</v>
+      </c>
+      <c r="U23" t="n">
+        <v>41</v>
+      </c>
+      <c r="V23" t="n">
+        <v>57</v>
+      </c>
+      <c r="W23" t="n">
+        <v>13</v>
+      </c>
+      <c r="X23" t="n">
         <v>8</v>
       </c>
-      <c r="N23" t="n">
-        <v>22</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>50</v>
-      </c>
-      <c r="R23" t="n">
-        <v>88</v>
-      </c>
-      <c r="S23" t="n">
-        <v>122</v>
-      </c>
-      <c r="T23" t="n">
-        <v>392</v>
-      </c>
-      <c r="U23" t="n">
-        <v>35</v>
-      </c>
-      <c r="V23" t="n">
-        <v>50</v>
-      </c>
-      <c r="W23" t="n">
-        <v>8</v>
-      </c>
-      <c r="X23" t="n">
-        <v>5</v>
-      </c>
       <c r="Y23" t="n">
-        <v>168</v>
+        <v>199</v>
       </c>
       <c r="Z23" t="n">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.848</v>
+        <v>0.836</v>
       </c>
       <c r="AB23" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="AC23" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.548</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AE23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF23" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.238</v>
+        <v>0.269</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
@@ -3919,41 +3919,41 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>517:31</t>
+          <t>610:20</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>267.24</v>
+        <v>320.72</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.649</v>
+        <v>0.672</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.725</v>
+        <v>0.731</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.179</v>
+        <v>1.188</v>
       </c>
       <c r="AS23" t="n">
         <v>0.187</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.622</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AU23" t="n">
-        <v>0.36</v>
+        <v>0.383</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.239</v>
+        <v>0.243</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.099</v>
+        <v>0.103</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.172</v>
+        <v>0.166</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.027</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="24">
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -3990,10 +3990,10 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="L24" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -4005,7 +4005,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4118,157 +4118,157 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>2765</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1103</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>917</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>603</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>758</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>523</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>767</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>453</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>431</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>747</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>721</v>
       </c>
       <c r="T25" t="n">
-        <v>73</v>
+        <v>2995</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>322</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>926</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1199</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>0.772</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>0.416</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>0.351</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>726</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>0.369</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>6500:00</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>20</v>
+        <v>2806.52</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>0.535</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>0.587</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>0.985</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>0.299</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>1.155</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
@@ -4277,157 +4277,157 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C26" t="n">
-        <v>2409</v>
+        <v>2981</v>
       </c>
       <c r="D26" t="n">
-        <v>494</v>
+        <v>674</v>
       </c>
       <c r="E26" t="n">
-        <v>960</v>
+        <v>1144</v>
       </c>
       <c r="F26" t="n">
-        <v>291</v>
+        <v>343</v>
       </c>
       <c r="G26" t="n">
-        <v>800</v>
+        <v>999</v>
       </c>
       <c r="H26" t="n">
-        <v>548</v>
+        <v>604</v>
       </c>
       <c r="I26" t="n">
-        <v>689</v>
+        <v>808</v>
       </c>
       <c r="J26" t="n">
-        <v>454</v>
+        <v>615</v>
       </c>
       <c r="K26" t="n">
-        <v>663</v>
+        <v>780</v>
       </c>
       <c r="L26" t="n">
-        <v>293</v>
+        <v>389</v>
       </c>
       <c r="M26" t="n">
-        <v>176</v>
+        <v>257</v>
       </c>
       <c r="N26" t="n">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="Q26" t="n">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="R26" t="n">
-        <v>653</v>
+        <v>721</v>
       </c>
       <c r="S26" t="n">
-        <v>639</v>
+        <v>747</v>
       </c>
       <c r="T26" t="n">
-        <v>2584</v>
+        <v>3473</v>
       </c>
       <c r="U26" t="n">
-        <v>289</v>
+        <v>368</v>
       </c>
       <c r="V26" t="n">
-        <v>307</v>
+        <v>398</v>
       </c>
       <c r="W26" t="n">
-        <v>150</v>
+        <v>224</v>
       </c>
       <c r="X26" t="n">
+        <v>127</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1319</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>186</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>374</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>92</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>259</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AH26" t="n">
         <v>89</v>
       </c>
-      <c r="Y26" t="n">
-        <v>816</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1061</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0.769</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>141</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>342</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>246</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>58</v>
-      </c>
       <c r="AI26" t="n">
-        <v>170</v>
+        <v>240</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.341</v>
+        <v>0.371</v>
       </c>
       <c r="AK26" t="n">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="AL26" t="n">
-        <v>630</v>
+        <v>759</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.37</v>
+        <v>0.335</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>5700:00</t>
+          <t>6500:00</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>2462.16</v>
+        <v>2889.52</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.529</v>
+        <v>0.555</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.584</v>
+        <v>0.597</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.978</v>
+        <v>1.032</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.162</v>
+        <v>0.135</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.311</v>
+        <v>0.282</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.138</v>
+        <v>1.573</v>
       </c>
       <c r="AV26" t="n">
         <v>0.2</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.06</v>
+        <v>0.067</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.132</v>
+        <v>0.14</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
@@ -4436,2440 +4436,2440 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>28</v>
-      </c>
-      <c r="C27" t="n">
-        <v>2612</v>
-      </c>
-      <c r="D27" t="n">
-        <v>587</v>
-      </c>
-      <c r="E27" t="n">
-        <v>982</v>
-      </c>
-      <c r="F27" t="n">
-        <v>303</v>
-      </c>
-      <c r="G27" t="n">
-        <v>879</v>
-      </c>
-      <c r="H27" t="n">
-        <v>529</v>
-      </c>
-      <c r="I27" t="n">
-        <v>716</v>
-      </c>
-      <c r="J27" t="n">
-        <v>544</v>
-      </c>
-      <c r="K27" t="n">
-        <v>689</v>
-      </c>
-      <c r="L27" t="n">
-        <v>338</v>
-      </c>
-      <c r="M27" t="n">
-        <v>218</v>
-      </c>
-      <c r="N27" t="n">
-        <v>123</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>352</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>329</v>
-      </c>
-      <c r="R27" t="n">
-        <v>639</v>
-      </c>
-      <c r="S27" t="n">
-        <v>654</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3029</v>
-      </c>
-      <c r="U27" t="n">
-        <v>327</v>
-      </c>
-      <c r="V27" t="n">
-        <v>344</v>
-      </c>
-      <c r="W27" t="n">
-        <v>197</v>
-      </c>
-      <c r="X27" t="n">
-        <v>110</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>871</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1151</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0.757</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>167</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>323</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0.517</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>78</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>224</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0.348</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>84</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>211</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0.398</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>219</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>668</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0.328</v>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>5700:00</t>
-        </is>
-      </c>
-      <c r="AO27" t="n">
-        <v>2528.04</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.033</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0.284</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>1.545</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="inlineStr"/>
-      <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="inlineStr"/>
-      <c r="AO28" t="inlineStr"/>
-      <c r="AP28" t="inlineStr"/>
-      <c r="AQ28" t="inlineStr"/>
-      <c r="AR28" t="inlineStr"/>
-      <c r="AS28" t="inlineStr"/>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AU28" t="inlineStr"/>
-      <c r="AV28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr"/>
-      <c r="AX28" t="inlineStr"/>
-      <c r="AY28" t="inlineStr"/>
+          <t>#00 M. UDEZE (Per Game)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>21</v>
+      </c>
+      <c r="C28" t="n">
+        <v>5.714</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.095</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.714</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.857</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.476</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.143</v>
+      </c>
+      <c r="T28" t="n">
+        <v>139</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.238</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>3.286</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4.857</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AO28" t="n">
+        <v>5.284</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.081</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0.011</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>#00 M. UDEZE (Per Game)</t>
+          <t>#0 S. EVANS (Per Game)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C29" t="n">
-        <v>5.714</v>
+        <v>13.033</v>
       </c>
       <c r="D29" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5.467</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3.567</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5.633</v>
+      </c>
+      <c r="K29" t="n">
         <v>2</v>
       </c>
-      <c r="E29" t="n">
-        <v>3.095</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1.714</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1.857</v>
-      </c>
       <c r="L29" t="n">
-        <v>1.19</v>
+        <v>0.367</v>
       </c>
       <c r="M29" t="n">
-        <v>0.571</v>
+        <v>1.233</v>
       </c>
       <c r="N29" t="n">
-        <v>0.476</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0.952</v>
+        <v>3.167</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.952</v>
+        <v>3.167</v>
       </c>
       <c r="R29" t="n">
-        <v>2.476</v>
+        <v>2</v>
       </c>
       <c r="S29" t="n">
-        <v>2.143</v>
+        <v>4.633</v>
       </c>
       <c r="T29" t="n">
-        <v>139</v>
+        <v>444</v>
       </c>
       <c r="U29" t="n">
-        <v>0.571</v>
+        <v>1.7</v>
       </c>
       <c r="V29" t="n">
-        <v>1.238</v>
+        <v>0.8</v>
       </c>
       <c r="W29" t="n">
-        <v>0.095</v>
+        <v>1.2</v>
       </c>
       <c r="X29" t="n">
-        <v>0.095</v>
+        <v>0.733</v>
       </c>
       <c r="Y29" t="n">
-        <v>3.286</v>
+        <v>4.967</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.857</v>
+        <v>6.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.676</v>
+        <v>0.741</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.381</v>
+        <v>0.633</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.952</v>
+        <v>2.033</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.4</v>
+        <v>0.311</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.048</v>
+        <v>0.2</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.095</v>
+        <v>0.767</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.5</v>
+        <v>0.261</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.633</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>5.333</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>0.306</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>25:52</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>5.284</v>
+        <v>15.725</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.646</v>
+        <v>0.444</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.66</v>
+        <v>0.519</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.081</v>
+        <v>0.829</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.18</v>
+        <v>0.201</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.554</v>
+        <v>0.334</v>
       </c>
       <c r="AU29" t="n">
-        <v>0.3</v>
+        <v>1.779</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.186</v>
+        <v>0.282</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.105</v>
+        <v>0.016</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.161</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.011</v>
+        <v>0.228</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>#0 S. EVANS (Per Game)</t>
+          <t>#1 X. CASTAÑEDA (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C30" t="n">
-        <v>13</v>
+        <v>11.125</v>
       </c>
       <c r="D30" t="n">
-        <v>2.231</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>5.308</v>
+        <v>3.875</v>
       </c>
       <c r="F30" t="n">
-        <v>1.577</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
-        <v>5.346</v>
+        <v>5.25</v>
       </c>
       <c r="H30" t="n">
-        <v>3.808</v>
+        <v>3.125</v>
       </c>
       <c r="I30" t="n">
-        <v>4.615</v>
+        <v>3.875</v>
       </c>
       <c r="J30" t="n">
-        <v>5.692</v>
+        <v>2.25</v>
       </c>
       <c r="K30" t="n">
-        <v>1.885</v>
+        <v>1.625</v>
       </c>
       <c r="L30" t="n">
-        <v>0.385</v>
+        <v>0.125</v>
       </c>
       <c r="M30" t="n">
-        <v>1.269</v>
+        <v>0.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.615</v>
+        <v>0.125</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.154</v>
+        <v>1.875</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.154</v>
+        <v>1.875</v>
       </c>
       <c r="R30" t="n">
-        <v>2.038</v>
+        <v>2</v>
       </c>
       <c r="S30" t="n">
-        <v>4.577</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
-        <v>379</v>
+        <v>68</v>
       </c>
       <c r="U30" t="n">
-        <v>1.962</v>
+        <v>1.125</v>
       </c>
       <c r="V30" t="n">
-        <v>0.8080000000000001</v>
+        <v>1.125</v>
       </c>
       <c r="W30" t="n">
-        <v>0.885</v>
+        <v>1.25</v>
       </c>
       <c r="X30" t="n">
-        <v>0.538</v>
+        <v>1.125</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.115</v>
+        <v>3.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>7</v>
+        <v>4.25</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.731</v>
+        <v>0.765</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.731</v>
+        <v>0.125</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.231</v>
+        <v>1.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.328</v>
+        <v>0.083</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.192</v>
+        <v>0.75</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.6919999999999999</v>
+        <v>2</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.278</v>
+        <v>0.375</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.038</v>
+        <v>0.125</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.154</v>
+        <v>0.5</v>
       </c>
       <c r="AJ30" t="n">
         <v>0.25</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.538</v>
+        <v>1.875</v>
       </c>
       <c r="AL30" t="n">
-        <v>5.192</v>
+        <v>4.75</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.296</v>
+        <v>0.395</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>26:02</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>15.838</v>
+        <v>12.705</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.431</v>
+        <v>0.438</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.512</v>
+        <v>0.514</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.821</v>
+        <v>0.876</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.199</v>
+        <v>0.148</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.357</v>
+        <v>0.342</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.805</v>
+        <v>1.2</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.282</v>
+        <v>0.337</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.017</v>
+        <v>0.008</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.082</v>
+        <v>0.105</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.235</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#1 X. CASTAÑEDA (Per Game)</t>
+          <t>#3 A. BEST (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C31" t="n">
-        <v>11.125</v>
+        <v>8.75</v>
       </c>
       <c r="D31" t="n">
+        <v>1.219</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.938</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3.781</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.906</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.156</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="T31" t="n">
+        <v>207</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>2.438</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AK31" t="n">
         <v>1</v>
       </c>
-      <c r="E31" t="n">
-        <v>3.875</v>
-      </c>
-      <c r="F31" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="H31" t="n">
-        <v>3.125</v>
-      </c>
-      <c r="I31" t="n">
-        <v>3.875</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1.625</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.875</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.875</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T31" t="n">
-        <v>68</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.875</v>
-      </c>
       <c r="AL31" t="n">
-        <v>4.75</v>
+        <v>2.688</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.395</v>
+        <v>0.372</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>12.705</v>
+        <v>8.574</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.438</v>
+        <v>0.509</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.514</v>
+        <v>0.571</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.876</v>
+        <v>1.021</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.148</v>
+        <v>0.106</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.342</v>
+        <v>0.284</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.2</v>
+        <v>1.276</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.337</v>
+        <v>0.187</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.008</v>
+        <v>0.036</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.106</v>
+        <v>0.075</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.09</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#3 A. BEST (Per Game)</t>
+          <t>#5 R. LUZ (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C32" t="n">
-        <v>9.071</v>
+        <v>4.769</v>
       </c>
       <c r="D32" t="n">
-        <v>1.107</v>
+        <v>1.038</v>
       </c>
       <c r="E32" t="n">
-        <v>2.821</v>
+        <v>1.692</v>
       </c>
       <c r="F32" t="n">
-        <v>1.643</v>
+        <v>0.5</v>
       </c>
       <c r="G32" t="n">
-        <v>4</v>
+        <v>0.962</v>
       </c>
       <c r="H32" t="n">
-        <v>1.929</v>
+        <v>1.192</v>
       </c>
       <c r="I32" t="n">
-        <v>2.214</v>
+        <v>1.615</v>
       </c>
       <c r="J32" t="n">
-        <v>1.179</v>
+        <v>3.269</v>
       </c>
       <c r="K32" t="n">
-        <v>1.393</v>
+        <v>2.038</v>
       </c>
       <c r="L32" t="n">
-        <v>0.607</v>
+        <v>0.654</v>
       </c>
       <c r="M32" t="n">
-        <v>0.429</v>
+        <v>0.538</v>
       </c>
       <c r="N32" t="n">
-        <v>0.179</v>
+        <v>0.231</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.893</v>
+        <v>1.615</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.893</v>
+        <v>1.615</v>
       </c>
       <c r="R32" t="n">
-        <v>2.643</v>
+        <v>1.731</v>
       </c>
       <c r="S32" t="n">
-        <v>1.714</v>
+        <v>1.462</v>
       </c>
       <c r="T32" t="n">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="U32" t="n">
-        <v>1.357</v>
+        <v>0.423</v>
       </c>
       <c r="V32" t="n">
-        <v>0.821</v>
+        <v>1.192</v>
       </c>
       <c r="W32" t="n">
-        <v>0.857</v>
+        <v>0.308</v>
       </c>
       <c r="X32" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.615</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="AF32" t="n">
         <v>0.5</v>
       </c>
-      <c r="Y32" t="n">
-        <v>2.357</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.964</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0.321</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0.964</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.107</v>
-      </c>
       <c r="AG32" t="n">
-        <v>0.323</v>
+        <v>0.538</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.536</v>
+        <v>0.038</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.214</v>
+        <v>0.077</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.441</v>
+        <v>0.5</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.107</v>
+        <v>0.462</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.786</v>
+        <v>0.885</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.397</v>
+        <v>0.522</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>8.689</v>
+        <v>4.98</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.524</v>
+        <v>0.674</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.582</v>
+        <v>0.709</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.044</v>
+        <v>0.958</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.103</v>
+        <v>0.324</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.283</v>
+        <v>0.449</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.32</v>
+        <v>2.024</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.187</v>
+        <v>0.147</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.033</v>
+        <v>0.048</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.074</v>
+        <v>0.146</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.047</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#5 R. LUZ (Per Game)</t>
+          <t>#8 A. GANAL (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C33" t="n">
-        <v>4.545</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>1.545</v>
+        <v>0.077</v>
       </c>
       <c r="F33" t="n">
-        <v>0.409</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.636</v>
+        <v>0.231</v>
       </c>
       <c r="H33" t="n">
-        <v>1.318</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1.727</v>
+        <v>0.154</v>
       </c>
       <c r="J33" t="n">
-        <v>3.045</v>
+        <v>0.154</v>
       </c>
       <c r="K33" t="n">
-        <v>1.864</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="M33" t="n">
-        <v>0.455</v>
+        <v>0.077</v>
       </c>
       <c r="N33" t="n">
-        <v>0.182</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.682</v>
+        <v>0.077</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.682</v>
+        <v>0.077</v>
       </c>
       <c r="R33" t="n">
-        <v>1.773</v>
+        <v>0.077</v>
       </c>
       <c r="S33" t="n">
-        <v>1.545</v>
+        <v>0.077</v>
       </c>
       <c r="T33" t="n">
-        <v>169</v>
+        <v>-3</v>
       </c>
       <c r="U33" t="n">
-        <v>0.318</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.227</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0.364</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.818</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.364</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.769</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.5</v>
+        <v>0.231</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.545</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.227</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.409</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.045</v>
+        <v>0.077</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.364</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.591</v>
+        <v>0.154</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.615</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>00:38</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>4.624</v>
+        <v>0.452</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.773</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.983</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.364</v>
+        <v>0.17</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.604</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.811</v>
+        <v>2</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.144</v>
+        <v>0.331</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.053</v>
+        <v>0.141</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.142</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.114</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#8 A. GANAL (Per Game)</t>
+          <t>#10 J. RICE (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>13.583</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>3.333</v>
       </c>
       <c r="E34" t="n">
-        <v>0.077</v>
+        <v>6.417</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G34" t="n">
-        <v>0.231</v>
+        <v>3.75</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>2.417</v>
       </c>
       <c r="I34" t="n">
-        <v>0.154</v>
+        <v>3.333</v>
       </c>
       <c r="J34" t="n">
-        <v>0.154</v>
+        <v>4.167</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L34" t="n">
-        <v>0.077</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>0.077</v>
+        <v>0.583</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>0.917</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.077</v>
+        <v>2.667</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.077</v>
+        <v>2.667</v>
       </c>
       <c r="R34" t="n">
-        <v>0.077</v>
+        <v>2.583</v>
       </c>
       <c r="S34" t="n">
-        <v>0.077</v>
+        <v>3.75</v>
       </c>
       <c r="T34" t="n">
-        <v>-3</v>
+        <v>186</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.917</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>0.917</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>5.417</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.231</v>
+        <v>2.917</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>0.457</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.417</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>0.471</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.077</v>
+        <v>0.5</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.417</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.154</v>
+        <v>3.25</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>0.436</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>00:38</t>
+          <t>24:51</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>0.452</v>
+        <v>14.3</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>0.549</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>0.584</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.17</v>
+        <v>0.186</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>0.238</v>
       </c>
       <c r="AU34" t="n">
-        <v>2</v>
+        <v>1.563</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.331</v>
+        <v>0.266</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.141</v>
+        <v>0.047</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.005</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#10 J. RICE (Per Game)</t>
+          <t>#11 S. OKOYE (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C35" t="n">
-        <v>14.125</v>
+        <v>8.538</v>
       </c>
       <c r="D35" t="n">
-        <v>3.5</v>
+        <v>1.731</v>
       </c>
       <c r="E35" t="n">
-        <v>6.875</v>
+        <v>2.654</v>
       </c>
       <c r="F35" t="n">
-        <v>1.5</v>
+        <v>1.231</v>
       </c>
       <c r="G35" t="n">
-        <v>3.75</v>
+        <v>4.038</v>
       </c>
       <c r="H35" t="n">
-        <v>2.625</v>
+        <v>1.385</v>
       </c>
       <c r="I35" t="n">
-        <v>3.875</v>
+        <v>1.692</v>
       </c>
       <c r="J35" t="n">
-        <v>5.25</v>
+        <v>1.077</v>
       </c>
       <c r="K35" t="n">
-        <v>3.625</v>
+        <v>2.769</v>
       </c>
       <c r="L35" t="n">
-        <v>1.125</v>
+        <v>0.731</v>
       </c>
       <c r="M35" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="N35" t="n">
         <v>0.5</v>
       </c>
-      <c r="N35" t="n">
-        <v>0.875</v>
-      </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>3.125</v>
+        <v>0.885</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.125</v>
+        <v>0.885</v>
       </c>
       <c r="R35" t="n">
-        <v>3.125</v>
+        <v>2.462</v>
       </c>
       <c r="S35" t="n">
-        <v>4.125</v>
+        <v>1.231</v>
       </c>
       <c r="T35" t="n">
-        <v>132</v>
+        <v>216</v>
       </c>
       <c r="U35" t="n">
-        <v>2</v>
+        <v>1.462</v>
       </c>
       <c r="V35" t="n">
-        <v>2</v>
+        <v>1.192</v>
       </c>
       <c r="W35" t="n">
-        <v>1.875</v>
+        <v>0.615</v>
       </c>
       <c r="X35" t="n">
-        <v>1.125</v>
+        <v>0.346</v>
       </c>
       <c r="Y35" t="n">
-        <v>3.875</v>
+        <v>2.231</v>
       </c>
       <c r="Z35" t="n">
-        <v>6</v>
+        <v>2.885</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.646</v>
+        <v>0.773</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.5</v>
+        <v>0.462</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.25</v>
+        <v>0.885</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.462</v>
+        <v>0.522</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.75</v>
+        <v>0.423</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.5</v>
+        <v>0.577</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.5</v>
+        <v>0.733</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.125</v>
+        <v>0.423</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.625</v>
+        <v>1.462</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.2</v>
+        <v>0.289</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.375</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="AL35" t="n">
-        <v>3.125</v>
+        <v>2.577</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.44</v>
+        <v>0.313</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>27:18</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>15.455</v>
+        <v>8.321999999999999</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.541</v>
+        <v>0.534</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.573</v>
+        <v>0.574</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.914</v>
+        <v>1.026</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.202</v>
+        <v>0.106</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.247</v>
+        <v>0.207</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.68</v>
+        <v>1.217</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.262</v>
+        <v>0.178</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.048</v>
+        <v>0.039</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.151</v>
+        <v>0.144</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.228</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#11 S. OKOYE (Per Game)</t>
+          <t>#13 C. ORTEGA (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C36" t="n">
-        <v>8.864000000000001</v>
+        <v>1.812</v>
       </c>
       <c r="D36" t="n">
-        <v>1.818</v>
+        <v>0.25</v>
       </c>
       <c r="E36" t="n">
-        <v>2.773</v>
+        <v>0.906</v>
       </c>
       <c r="F36" t="n">
-        <v>1.273</v>
+        <v>0.25</v>
       </c>
       <c r="G36" t="n">
-        <v>4.273</v>
+        <v>1.031</v>
       </c>
       <c r="H36" t="n">
-        <v>1.409</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>1.727</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>1.045</v>
+        <v>0.531</v>
       </c>
       <c r="K36" t="n">
-        <v>2.773</v>
+        <v>1.562</v>
       </c>
       <c r="L36" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.469</v>
       </c>
       <c r="M36" t="n">
-        <v>0.864</v>
+        <v>0.625</v>
       </c>
       <c r="N36" t="n">
-        <v>0.545</v>
+        <v>0.094</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.909</v>
+        <v>0.344</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.909</v>
+        <v>0.344</v>
       </c>
       <c r="R36" t="n">
-        <v>2.409</v>
+        <v>1.344</v>
       </c>
       <c r="S36" t="n">
-        <v>1.318</v>
+        <v>0.781</v>
       </c>
       <c r="T36" t="n">
-        <v>190</v>
+        <v>84</v>
       </c>
       <c r="U36" t="n">
-        <v>1.273</v>
+        <v>0.25</v>
       </c>
       <c r="V36" t="n">
-        <v>1.318</v>
+        <v>0.25</v>
       </c>
       <c r="W36" t="n">
-        <v>0.636</v>
+        <v>0.312</v>
       </c>
       <c r="X36" t="n">
-        <v>0.318</v>
+        <v>0.156</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.227</v>
+        <v>0.625</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.864</v>
+        <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.778</v>
+        <v>0.625</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.5</v>
+        <v>0.125</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.955</v>
+        <v>0.375</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.524</v>
+        <v>0.333</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.5</v>
+        <v>0.062</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.219</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.733</v>
+        <v>0.286</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.409</v>
+        <v>0.156</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.5</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AJ36" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AM36" t="n">
         <v>0.273</v>
       </c>
-      <c r="AK36" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>2.773</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0.311</v>
-      </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>22:17</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>8.715</v>
+        <v>2.584</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.529</v>
+        <v>0.323</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.405</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.017</v>
+        <v>0.701</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.104</v>
+        <v>0.133</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.2</v>
+        <v>0.29</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.15</v>
+        <v>1.545</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.181</v>
+        <v>0.101</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.043</v>
+        <v>0.046</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.142</v>
+        <v>0.148</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.042</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#13 C. ORTEGA (Per Game)</t>
+          <t>#15 K. KOSTADINOV (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C37" t="n">
+        <v>4.273</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1.636</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2.636</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.227</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="R37" t="n">
         <v>2</v>
       </c>
-      <c r="D37" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.036</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1.107</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1.714</v>
-      </c>
-      <c r="L37" t="n">
+      <c r="S37" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="T37" t="n">
+        <v>103</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.136</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.682</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AF37" t="n">
         <v>0.5</v>
       </c>
-      <c r="M37" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.536</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0.857</v>
-      </c>
-      <c r="T37" t="n">
-        <v>79</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0.643</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.071</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AB37" t="n">
+      <c r="AG37" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AM37" t="n">
         <v>0.143</v>
       </c>
-      <c r="AC37" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0.238</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0.3</v>
-      </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>2.814</v>
+        <v>4.536</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.333</v>
+        <v>0.596</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.407</v>
+        <v>0.612</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.711</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.127</v>
+        <v>0.23</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.267</v>
+        <v>0.191</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.6</v>
+        <v>0.522</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.099</v>
+        <v>0.155</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.044</v>
+        <v>0.106</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.149</v>
+        <v>0.11</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#15 K. KOSTADINOV (Per Game)</t>
+          <t>#20 F. BASSAS (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C38" t="n">
-        <v>3.833</v>
+        <v>1.2</v>
       </c>
       <c r="D38" t="n">
-        <v>1.444</v>
+        <v>0.2</v>
       </c>
       <c r="E38" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="F38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T38" t="n">
+        <v>17</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>05:10</t>
+        </is>
+      </c>
+      <c r="AO38" t="n">
+        <v>2.088</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="AT38" t="n">
         <v>0.167</v>
       </c>
-      <c r="G38" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1.222</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1.056</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0.278</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0.611</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.111</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.111</v>
-      </c>
-      <c r="R38" t="n">
-        <v>2</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1.111</v>
-      </c>
-      <c r="T38" t="n">
-        <v>67</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.778</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0.762</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AO38" t="n">
-        <v>4.509</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>0.246</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0.145</v>
-      </c>
       <c r="AU38" t="n">
-        <v>0.45</v>
+        <v>1</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.155</v>
+        <v>0.187</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.091</v>
+        <v>0.068</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.103</v>
+        <v>0.109</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.019</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#20 F. BASSAS (Per Game)</t>
+          <t>#22 J. MCKOY (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C39" t="n">
-        <v>1.2</v>
+        <v>6.533</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2</v>
+        <v>1.033</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5</v>
+        <v>2.467</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2</v>
+        <v>1.033</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7</v>
+        <v>3.433</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2</v>
+        <v>1.367</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2</v>
+        <v>1.533</v>
       </c>
       <c r="J39" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.033</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="T39" t="n">
+        <v>174</v>
+      </c>
+      <c r="U39" t="n">
         <v>0.8</v>
       </c>
-      <c r="K39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
+      <c r="V39" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.733</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="AA39" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="AB39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="AK39" t="n">
         <v>0.8</v>
       </c>
-      <c r="R39" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T39" t="n">
-        <v>17</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0.2</v>
-      </c>
       <c r="AL39" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>05:10</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>2.088</v>
+        <v>7.208</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.417</v>
+        <v>0.438</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.466</v>
+        <v>0.497</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.575</v>
+        <v>0.906</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.383</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.167</v>
+        <v>0.232</v>
       </c>
       <c r="AU39" t="n">
-        <v>1</v>
+        <v>0.895</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.187</v>
+        <v>0.19</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.067</v>
+        <v>0.064</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.029</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#22 J. MCKOY (Per Game)</t>
+          <t>#24 K. KURIC (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C40" t="n">
-        <v>7.077</v>
+        <v>11.367</v>
       </c>
       <c r="D40" t="n">
-        <v>1.115</v>
+        <v>1.633</v>
       </c>
       <c r="E40" t="n">
-        <v>2.692</v>
+        <v>4.067</v>
       </c>
       <c r="F40" t="n">
-        <v>1.115</v>
+        <v>2.033</v>
       </c>
       <c r="G40" t="n">
-        <v>3.5</v>
+        <v>4.367</v>
       </c>
       <c r="H40" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>1.692</v>
+        <v>2.3</v>
       </c>
       <c r="J40" t="n">
-        <v>0.615</v>
+        <v>1.2</v>
       </c>
       <c r="K40" t="n">
-        <v>2.154</v>
+        <v>1.633</v>
       </c>
       <c r="L40" t="n">
-        <v>1.038</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.467</v>
       </c>
       <c r="N40" t="n">
-        <v>0.154</v>
+        <v>0.333</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.867</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.867</v>
       </c>
       <c r="R40" t="n">
-        <v>1.538</v>
+        <v>1.533</v>
       </c>
       <c r="S40" t="n">
-        <v>1.269</v>
+        <v>2.167</v>
       </c>
       <c r="T40" t="n">
-        <v>172</v>
+        <v>308</v>
       </c>
       <c r="U40" t="n">
-        <v>0.923</v>
+        <v>0.633</v>
       </c>
       <c r="V40" t="n">
-        <v>0.923</v>
+        <v>1</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.885</v>
+        <v>2.533</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.346</v>
+        <v>3</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.803</v>
+        <v>0.844</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.423</v>
+        <v>0.4</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.885</v>
+        <v>1.067</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.478</v>
+        <v>0.375</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.308</v>
+        <v>0.7</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.154</v>
+        <v>2.3</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.267</v>
+        <v>0.304</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.231</v>
+        <v>0.5</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.577</v>
+        <v>0.833</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.885</v>
+        <v>1.533</v>
       </c>
       <c r="AL40" t="n">
-        <v>2.923</v>
+        <v>3.533</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.303</v>
+        <v>0.434</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>7.629</v>
+        <v>10.312</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.45</v>
+        <v>0.555</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.51</v>
+        <v>0.602</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.928</v>
+        <v>1.102</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.091</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.242</v>
+        <v>0.237</v>
       </c>
       <c r="AU40" t="n">
-        <v>0.889</v>
+        <v>1.385</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.197</v>
+        <v>0.223</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.067</v>
+        <v>0.031</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.137</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.024</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>#24 K. KURIC (Per Game)</t>
+          <t>#32 R. GUERRERO (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C41" t="n">
-        <v>11.615</v>
+        <v>1.969</v>
       </c>
       <c r="D41" t="n">
-        <v>1.731</v>
+        <v>0.719</v>
       </c>
       <c r="E41" t="n">
-        <v>4.269</v>
+        <v>1.094</v>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>4.385</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>2.154</v>
+        <v>0.531</v>
       </c>
       <c r="I41" t="n">
-        <v>2.462</v>
+        <v>0.75</v>
       </c>
       <c r="J41" t="n">
-        <v>1.346</v>
+        <v>0.25</v>
       </c>
       <c r="K41" t="n">
-        <v>1.615</v>
+        <v>1.156</v>
       </c>
       <c r="L41" t="n">
-        <v>0.538</v>
+        <v>0.75</v>
       </c>
       <c r="M41" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="T41" t="n">
+        <v>97</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AC41" t="n">
         <v>0.5</v>
       </c>
-      <c r="N41" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.462</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2.269</v>
-      </c>
-      <c r="T41" t="n">
-        <v>278</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.038</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>2.769</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>3.269</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0.847</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.154</v>
-      </c>
       <c r="AD41" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.654</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.308</v>
+        <v>0.031</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.283</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.423</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.731</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.579</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.577</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>3.654</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.432</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>22:12</t>
+          <t>07:09</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>10.622</v>
+        <v>1.643</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.547</v>
+        <v>0.657</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.596</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.094</v>
+        <v>1.199</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.083</v>
+        <v>0.133</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.249</v>
+        <v>0.486</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.522</v>
+        <v>1.143</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.221</v>
+        <v>0.106</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.028</v>
+        <v>0.122</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.083</v>
+        <v>0.182</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.055</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#32 R. GUERRERO (Per Game)</t>
+          <t>#35 Y. PONS (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>28</v>
       </c>
       <c r="C42" t="n">
-        <v>2.107</v>
+        <v>8.25</v>
       </c>
       <c r="D42" t="n">
-        <v>0.786</v>
+        <v>1.071</v>
       </c>
       <c r="E42" t="n">
-        <v>1.214</v>
+        <v>1.679</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1.857</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>4.429</v>
       </c>
       <c r="H42" t="n">
         <v>0.536</v>
       </c>
       <c r="I42" t="n">
-        <v>0.786</v>
+        <v>0.75</v>
       </c>
       <c r="J42" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.571</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T42" t="n">
+        <v>185</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="X42" t="n">
         <v>0.286</v>
-      </c>
-      <c r="K42" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0.821</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.143</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0.643</v>
-      </c>
-      <c r="T42" t="n">
-        <v>91</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0.07099999999999999</v>
       </c>
       <c r="Y42" t="n">
         <v>1.071</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.429</v>
+        <v>1.393</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.75</v>
+        <v>0.769</v>
       </c>
       <c r="AB42" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AH42" t="n">
         <v>0.25</v>
       </c>
-      <c r="AC42" t="n">
-        <v>0.536</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>1.107</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>0.226</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.607</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>3.321</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>0.484</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>1.81</v>
+        <v>7.151</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.647</v>
+        <v>0.632</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.675</v>
+        <v>0.641</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.164</v>
+        <v>1.154</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.138</v>
+        <v>0.1</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.441</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.143</v>
+        <v>0.35</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.108</v>
+        <v>0.147</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.123</v>
+        <v>0.03</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.184</v>
+        <v>0.116</v>
       </c>
       <c r="AY42" t="n">
         <v>0.01</v>
@@ -6878,263 +6878,263 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#35 Y. PONS (Per Game)</t>
+          <t>#99 A. PUSTOVYI (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C43" t="n">
-        <v>8.458</v>
+        <v>11.906</v>
       </c>
       <c r="D43" t="n">
-        <v>1.167</v>
+        <v>4.156</v>
       </c>
       <c r="E43" t="n">
-        <v>1.75</v>
+        <v>6.125</v>
       </c>
       <c r="F43" t="n">
-        <v>1.833</v>
+        <v>0.031</v>
       </c>
       <c r="G43" t="n">
-        <v>4.542</v>
+        <v>0.125</v>
       </c>
       <c r="H43" t="n">
-        <v>0.625</v>
+        <v>3.5</v>
       </c>
       <c r="I43" t="n">
-        <v>0.875</v>
+        <v>4.312</v>
       </c>
       <c r="J43" t="n">
-        <v>0.208</v>
+        <v>0.719</v>
       </c>
       <c r="K43" t="n">
-        <v>2.083</v>
+        <v>2.812</v>
       </c>
       <c r="L43" t="n">
-        <v>0.625</v>
+        <v>1.688</v>
       </c>
       <c r="M43" t="n">
-        <v>0.542</v>
+        <v>0.281</v>
       </c>
       <c r="N43" t="n">
-        <v>0.417</v>
+        <v>0.844</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.75</v>
+        <v>1.875</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.75</v>
+        <v>1.875</v>
       </c>
       <c r="R43" t="n">
-        <v>2.5</v>
+        <v>3.188</v>
       </c>
       <c r="S43" t="n">
-        <v>0.875</v>
+        <v>4.531</v>
       </c>
       <c r="T43" t="n">
-        <v>154</v>
+        <v>475</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>1.281</v>
       </c>
       <c r="V43" t="n">
-        <v>0.542</v>
+        <v>1.781</v>
       </c>
       <c r="W43" t="n">
-        <v>0.833</v>
+        <v>0.406</v>
       </c>
       <c r="X43" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.25</v>
+        <v>6.219</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.542</v>
+        <v>7.438</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.836</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.208</v>
+        <v>1.219</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.5</v>
+        <v>2.188</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.417</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.333</v>
+        <v>0.219</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.583</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.571</v>
+        <v>0.269</v>
       </c>
       <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AM43" t="n">
         <v>0.25</v>
       </c>
-      <c r="AI43" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0.207</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>1.583</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>0.475</v>
-      </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>22:21</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>7.427</v>
+        <v>10.022</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.623</v>
+        <v>0.672</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.633</v>
+        <v>0.731</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.139</v>
+        <v>1.188</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.101</v>
+        <v>0.187</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.099</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AU43" t="n">
-        <v>0.278</v>
+        <v>0.383</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.154</v>
+        <v>0.243</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.032</v>
+        <v>0.103</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.106</v>
+        <v>0.166</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.008</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#99 A. PUSTOVYI (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C44" t="n">
-        <v>11.25</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>5.714</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.036</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>3.643</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>4.321</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0.643</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>2.786</v>
+        <v>1.969</v>
       </c>
       <c r="L44" t="n">
-        <v>1.571</v>
+        <v>1.406</v>
       </c>
       <c r="M44" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>0.786</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1.786</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.786</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>3.143</v>
+        <v>0.031</v>
       </c>
       <c r="S44" t="n">
-        <v>4.357</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.786</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0.179</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>7.071</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.848</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.214</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.548</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.179</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.238</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
         <v>0</v>
@@ -7146,207 +7146,207 @@
         <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.036</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>9.544</v>
+        <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.649</v>
+        <v>0</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.725</v>
+        <v>0</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.179</v>
+        <v>0</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.187</v>
+        <v>0</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.622</v>
+        <v>0</v>
       </c>
       <c r="AU44" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.239</v>
+        <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.099</v>
+        <v>0</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.172</v>
+        <v>0</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>86.40600000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>18.125</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>34.469</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>10.438</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>28.656</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>18.844</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>23.688</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>16.344</v>
       </c>
       <c r="K45" t="n">
-        <v>2</v>
+        <v>23.969</v>
       </c>
       <c r="L45" t="n">
-        <v>1.357</v>
+        <v>10.531</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>6.281</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.438</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.714</v>
+        <v>14.156</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>13.469</v>
       </c>
       <c r="R45" t="n">
-        <v>0.036</v>
+        <v>23.344</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>22.531</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2995</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>10.062</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>10.875</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>5.719</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>3.438</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>28.938</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>37.469</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>0.772</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>4.938</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>11.875</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>0.416</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>3.094</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>8.811999999999999</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>0.351</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>2.062</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>5.969</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>8.375</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>22.688</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>0.369</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>203:07</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>0</v>
+        <v>87.70399999999999</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>0.535</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>0.587</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>0.985</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>0.299</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>1.155</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="AY45" t="n">
         <v>0</v>
@@ -7355,477 +7355,159 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>93.15600000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>21.062</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>35.75</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>10.719</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>31.219</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>18.875</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>25.25</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>19.219</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>24.375</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>12.156</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>8.031000000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>4.562</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>12.219</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>11.469</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>22.531</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>23.344</v>
       </c>
       <c r="T46" t="n">
-        <v>73</v>
+        <v>3473</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>12.438</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>3.969</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>31.25</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>41.219</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>0.758</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>5.812</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>11.688</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>0.497</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>2.875</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>8.093999999999999</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>0.355</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>2.781</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>0.371</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>7.938</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>23.719</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>0.335</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>203:07</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>0.714</v>
+        <v>90.298</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>0.555</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>0.597</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>1.032</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>0.282</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>1.573</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>0.206</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>28</v>
-      </c>
-      <c r="C47" t="n">
-        <v>86.036</v>
-      </c>
-      <c r="D47" t="n">
-        <v>17.643</v>
-      </c>
-      <c r="E47" t="n">
-        <v>34.286</v>
-      </c>
-      <c r="F47" t="n">
-        <v>10.393</v>
-      </c>
-      <c r="G47" t="n">
-        <v>28.571</v>
-      </c>
-      <c r="H47" t="n">
-        <v>19.571</v>
-      </c>
-      <c r="I47" t="n">
-        <v>24.607</v>
-      </c>
-      <c r="J47" t="n">
-        <v>16.214</v>
-      </c>
-      <c r="K47" t="n">
-        <v>23.679</v>
-      </c>
-      <c r="L47" t="n">
-        <v>10.464</v>
-      </c>
-      <c r="M47" t="n">
-        <v>6.286</v>
-      </c>
-      <c r="N47" t="n">
-        <v>4.214</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>14.25</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>13.536</v>
-      </c>
-      <c r="R47" t="n">
-        <v>23.321</v>
-      </c>
-      <c r="S47" t="n">
-        <v>22.821</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2584</v>
-      </c>
-      <c r="U47" t="n">
-        <v>10.321</v>
-      </c>
-      <c r="V47" t="n">
-        <v>10.964</v>
-      </c>
-      <c r="W47" t="n">
-        <v>5.357</v>
-      </c>
-      <c r="X47" t="n">
-        <v>3.179</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>29.143</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>37.893</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0.769</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>5.036</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>12.214</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>3.036</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>8.786</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>2.071</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>6.071</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>8.321</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>203:34</t>
-        </is>
-      </c>
-      <c r="AO47" t="n">
-        <v>87.934</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>0.978</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>0.162</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>0.311</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>1.138</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>28</v>
-      </c>
-      <c r="C48" t="n">
-        <v>93.286</v>
-      </c>
-      <c r="D48" t="n">
-        <v>20.964</v>
-      </c>
-      <c r="E48" t="n">
-        <v>35.071</v>
-      </c>
-      <c r="F48" t="n">
-        <v>10.821</v>
-      </c>
-      <c r="G48" t="n">
-        <v>31.393</v>
-      </c>
-      <c r="H48" t="n">
-        <v>18.893</v>
-      </c>
-      <c r="I48" t="n">
-        <v>25.571</v>
-      </c>
-      <c r="J48" t="n">
-        <v>19.429</v>
-      </c>
-      <c r="K48" t="n">
-        <v>24.607</v>
-      </c>
-      <c r="L48" t="n">
-        <v>12.071</v>
-      </c>
-      <c r="M48" t="n">
-        <v>7.786</v>
-      </c>
-      <c r="N48" t="n">
-        <v>4.393</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>12.571</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="R48" t="n">
-        <v>22.821</v>
-      </c>
-      <c r="S48" t="n">
-        <v>23.357</v>
-      </c>
-      <c r="T48" t="n">
-        <v>3029</v>
-      </c>
-      <c r="U48" t="n">
-        <v>11.679</v>
-      </c>
-      <c r="V48" t="n">
-        <v>12.286</v>
-      </c>
-      <c r="W48" t="n">
-        <v>7.036</v>
-      </c>
-      <c r="X48" t="n">
-        <v>3.929</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>31.107</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>41.107</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0.757</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>5.964</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>11.536</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0.517</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>2.786</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>0.348</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>7.536</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0.398</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>7.821</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>23.857</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>0.328</v>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>203:34</t>
-        </is>
-      </c>
-      <c r="AO48" t="n">
-        <v>90.28700000000001</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>1.033</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>0.284</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>1.545</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="AY48" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_MoraBanc Andorra.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_MoraBanc Andorra.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2469.52</v>
+        <v>2635.08</v>
       </c>
       <c r="C2" t="n">
-        <v>2485.02</v>
+        <v>2649.84</v>
       </c>
       <c r="D2" t="n">
-        <v>111.2667101270815</v>
+        <v>112.3086676931437</v>
       </c>
       <c r="E2" t="n">
-        <v>119.9587930881844</v>
+        <v>119.5921263170607</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5351485148514852</v>
+        <v>0.5393154486586494</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1614098598976669</v>
+        <v>0.1618338505800711</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3017009847806625</v>
+        <v>0.3095037846930194</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2985148514851485</v>
+        <v>0.2978723404255319</v>
       </c>
       <c r="J2" t="n">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="K2" t="n">
-        <v>348</v>
+        <v>389</v>
       </c>
       <c r="L2" t="n">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="M2" t="n">
-        <v>431</v>
+        <v>462</v>
       </c>
       <c r="N2" t="n">
-        <v>926</v>
+        <v>994</v>
       </c>
       <c r="O2" t="n">
-        <v>1199</v>
+        <v>1280</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5935643564356435</v>
+        <v>0.5920444033302498</v>
       </c>
       <c r="Q2" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="R2" t="n">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1881188118811881</v>
+        <v>0.1817761332099908</v>
       </c>
       <c r="T2" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="U2" t="n">
-        <v>282</v>
+        <v>312</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1396039603960396</v>
+        <v>0.1443108233117484</v>
       </c>
       <c r="W2" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="X2" t="n">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09455445544554456</v>
+        <v>0.09713228492136911</v>
       </c>
       <c r="Z2" t="n">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="AA2" t="n">
-        <v>726</v>
+        <v>774</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3594059405940594</v>
+        <v>0.3580018501387604</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7723102585487907</v>
+        <v>0.7765625</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4157894736842105</v>
+        <v>0.4173027989821883</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.351063829787234</v>
+        <v>0.358974358974359</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3455497382198953</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3691460055096419</v>
+        <v>0.3720930232558139</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.544620517097581</v>
+        <v>1.553125</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.7021276595744681</v>
+        <v>0.717948717948718</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.092693565976009</v>
+        <v>1.097560975609756</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.8253588516746412</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.032640949554896</v>
+        <v>1.057065217391304</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.663636363636364</v>
+        <v>1.631147540983606</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.154525386313466</v>
+        <v>1.139917695473251</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.459161147902869</v>
+        <v>4.448559670781893</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.613686534216336</v>
+        <v>5.588477366255144</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77.1725</v>
+        <v>77.50235294117648</v>
       </c>
       <c r="C3" t="n">
-        <v>77.656875</v>
+        <v>77.93647058823528</v>
       </c>
       <c r="D3" t="n">
-        <v>111.2667101270815</v>
+        <v>112.3086676931438</v>
       </c>
       <c r="E3" t="n">
-        <v>119.9587930881844</v>
+        <v>119.5921263170607</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5351485148514852</v>
+        <v>0.5393154486586494</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1614098598976669</v>
+        <v>0.1618338505800711</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3017009847806625</v>
+        <v>0.3095037846930194</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2985148514851485</v>
+        <v>0.2978723404255319</v>
       </c>
       <c r="J3" t="n">
-        <v>10.0625</v>
+        <v>10.14705882352941</v>
       </c>
       <c r="K3" t="n">
-        <v>10.875</v>
+        <v>11.44117647058824</v>
       </c>
       <c r="L3" t="n">
-        <v>5.71875</v>
+        <v>5.852941176470588</v>
       </c>
       <c r="M3" t="n">
-        <v>13.46875</v>
+        <v>13.58823529411765</v>
       </c>
       <c r="N3" t="n">
-        <v>28.9375</v>
+        <v>29.23529411764706</v>
       </c>
       <c r="O3" t="n">
-        <v>37.46875</v>
+        <v>37.64705882352941</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5935643564356435</v>
+        <v>0.5920444033302498</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.9375</v>
+        <v>4.823529411764706</v>
       </c>
       <c r="R3" t="n">
-        <v>11.875</v>
+        <v>11.55882352941176</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1881188118811881</v>
+        <v>0.1817761332099907</v>
       </c>
       <c r="T3" t="n">
-        <v>3.09375</v>
+        <v>3.294117647058823</v>
       </c>
       <c r="U3" t="n">
-        <v>8.8125</v>
+        <v>9.176470588235293</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1396039603960396</v>
+        <v>0.1443108233117484</v>
       </c>
       <c r="W3" t="n">
-        <v>2.0625</v>
+        <v>2.117647058823529</v>
       </c>
       <c r="X3" t="n">
-        <v>5.96875</v>
+        <v>6.176470588235294</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.09455445544554456</v>
+        <v>0.09713228492136911</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.375</v>
+        <v>8.470588235294118</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.6875</v>
+        <v>22.76470588235294</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3594059405940594</v>
+        <v>0.3580018501387604</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7723102585487907</v>
+        <v>0.7765624999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4157894736842105</v>
+        <v>0.4173027989821883</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.351063829787234</v>
+        <v>0.358974358974359</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3455497382198953</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3691460055096419</v>
+        <v>0.3720930232558139</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.544620517097581</v>
+        <v>1.553125</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.7021276595744681</v>
+        <v>0.717948717948718</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.092693565976009</v>
+        <v>1.097560975609756</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.8253588516746411</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.032640949554896</v>
+        <v>1.057065217391304</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.663636363636364</v>
+        <v>1.631147540983606</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.154525386313466</v>
+        <v>1.139917695473251</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.459161147902869</v>
+        <v>4.448559670781894</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.613686534216336</v>
+        <v>5.588477366255145</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2500.52</v>
+        <v>2664.6</v>
       </c>
       <c r="C4" t="n">
-        <v>2485.02</v>
+        <v>2649.84</v>
       </c>
       <c r="D4" t="n">
-        <v>119.9587930881844</v>
+        <v>119.5921263170607</v>
       </c>
       <c r="E4" t="n">
-        <v>111.2667101270815</v>
+        <v>112.3086676931437</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5545963602426505</v>
+        <v>0.5528277071459886</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1353165923752042</v>
+        <v>0.1357319132354851</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3365051903114187</v>
+        <v>0.3354890864995958</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2818478768082128</v>
+        <v>0.283647523016221</v>
       </c>
       <c r="J4" t="n">
-        <v>368</v>
+        <v>403</v>
       </c>
       <c r="K4" t="n">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="L4" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="M4" t="n">
-        <v>367</v>
+        <v>394</v>
       </c>
       <c r="N4" t="n">
-        <v>1000</v>
+        <v>1067</v>
       </c>
       <c r="O4" t="n">
-        <v>1319</v>
+        <v>1406</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6154923005132991</v>
+        <v>0.6163963174046471</v>
       </c>
       <c r="Q4" t="n">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="R4" t="n">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1745216985534298</v>
+        <v>0.1749232792634809</v>
       </c>
       <c r="T4" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="U4" t="n">
-        <v>259</v>
+        <v>287</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1208586094260383</v>
+        <v>0.1258220078912758</v>
       </c>
       <c r="W4" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="X4" t="n">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1119925338310779</v>
+        <v>0.1113546690048225</v>
       </c>
       <c r="Z4" t="n">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="AA4" t="n">
-        <v>759</v>
+        <v>800</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.354176388240784</v>
+        <v>0.3507233669443227</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7581501137225171</v>
+        <v>0.7588904694167852</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4973262032085561</v>
+        <v>0.4962406015037594</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3552123552123552</v>
+        <v>0.3484320557491289</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3708333333333333</v>
+        <v>0.3740157480314961</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3346508563899868</v>
+        <v>0.33375</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.516300227445034</v>
+        <v>1.51778093883357</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.7104247104247104</v>
+        <v>0.6968641114982579</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.03003003003003</v>
+        <v>1.030360531309298</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8123620309050773</v>
+        <v>0.8292181069958847</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.023136246786632</v>
+        <v>1.028915662650602</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.763779527559055</v>
+        <v>1.755555555555556</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.572890025575448</v>
+        <v>1.557416267942584</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.48081841432225</v>
+        <v>5.456937799043062</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.053708439897698</v>
+        <v>7.014354066985646</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78.14125</v>
+        <v>78.37058823529412</v>
       </c>
       <c r="C5" t="n">
-        <v>77.656875</v>
+        <v>77.93647058823528</v>
       </c>
       <c r="D5" t="n">
-        <v>119.9587930881844</v>
+        <v>119.5921263170607</v>
       </c>
       <c r="E5" t="n">
-        <v>111.2667101270815</v>
+        <v>112.3086676931438</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5545963602426505</v>
+        <v>0.5528277071459885</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1353165923752042</v>
+        <v>0.1357319132354851</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3365051903114187</v>
+        <v>0.3354890864995957</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2818478768082128</v>
+        <v>0.283647523016221</v>
       </c>
       <c r="J5" t="n">
-        <v>11.5</v>
+        <v>11.85294117647059</v>
       </c>
       <c r="K5" t="n">
-        <v>12.4375</v>
+        <v>12.55882352941176</v>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>6.970588235294118</v>
       </c>
       <c r="M5" t="n">
-        <v>11.46875</v>
+        <v>11.58823529411765</v>
       </c>
       <c r="N5" t="n">
-        <v>31.25</v>
+        <v>31.38235294117647</v>
       </c>
       <c r="O5" t="n">
-        <v>41.21875</v>
+        <v>41.35294117647059</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6154923005132991</v>
+        <v>0.6163963174046471</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.8125</v>
+        <v>5.823529411764706</v>
       </c>
       <c r="R5" t="n">
-        <v>11.6875</v>
+        <v>11.73529411764706</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1745216985534298</v>
+        <v>0.1749232792634809</v>
       </c>
       <c r="T5" t="n">
-        <v>2.875</v>
+        <v>2.941176470588236</v>
       </c>
       <c r="U5" t="n">
-        <v>8.09375</v>
+        <v>8.441176470588236</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1208586094260383</v>
+        <v>0.1258220078912758</v>
       </c>
       <c r="W5" t="n">
-        <v>2.78125</v>
+        <v>2.794117647058823</v>
       </c>
       <c r="X5" t="n">
-        <v>7.5</v>
+        <v>7.470588235294118</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1119925338310779</v>
+        <v>0.1113546690048224</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.9375</v>
+        <v>7.852941176470588</v>
       </c>
       <c r="AA5" t="n">
-        <v>23.71875</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.354176388240784</v>
+        <v>0.3507233669443227</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7581501137225171</v>
+        <v>0.7588904694167853</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4973262032085561</v>
+        <v>0.4962406015037594</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3552123552123552</v>
+        <v>0.3484320557491289</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3708333333333333</v>
+        <v>0.374015748031496</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3346508563899868</v>
+        <v>0.3337499999999999</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.516300227445034</v>
+        <v>1.517780938833571</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.7104247104247104</v>
+        <v>0.6968641114982579</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.03003003003003</v>
+        <v>1.030360531309298</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8123620309050773</v>
+        <v>0.8292181069958847</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.023136246786632</v>
+        <v>1.028915662650602</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.763779527559055</v>
+        <v>1.755555555555556</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.572890025575448</v>
+        <v>1.557416267942584</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.48081841432225</v>
+        <v>5.456937799043062</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.053708439897698</v>
+        <v>7.014354066985646</v>
       </c>
     </row>
     <row r="7">
@@ -1419,40 +1419,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>391</v>
+        <v>428</v>
       </c>
       <c r="D8" t="n">
+        <v>76</v>
+      </c>
+      <c r="E8" t="n">
+        <v>167</v>
+      </c>
+      <c r="F8" t="n">
+        <v>55</v>
+      </c>
+      <c r="G8" t="n">
+        <v>179</v>
+      </c>
+      <c r="H8" t="n">
+        <v>111</v>
+      </c>
+      <c r="I8" t="n">
+        <v>136</v>
+      </c>
+      <c r="J8" t="n">
+        <v>177</v>
+      </c>
+      <c r="K8" t="n">
         <v>67</v>
       </c>
-      <c r="E8" t="n">
-        <v>156</v>
-      </c>
-      <c r="F8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G8" t="n">
-        <v>164</v>
-      </c>
-      <c r="H8" t="n">
-        <v>107</v>
-      </c>
-      <c r="I8" t="n">
-        <v>129</v>
-      </c>
-      <c r="J8" t="n">
-        <v>169</v>
-      </c>
-      <c r="K8" t="n">
-        <v>60</v>
-      </c>
       <c r="L8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M8" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N8" t="n">
         <v>17</v>
@@ -1461,40 +1461,40 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="Q8" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="R8" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S8" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="T8" t="n">
-        <v>444</v>
+        <v>487</v>
       </c>
       <c r="U8" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="V8" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="W8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="X8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y8" t="n">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="Z8" t="n">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.741</v>
+        <v>0.737</v>
       </c>
       <c r="AB8" t="n">
         <v>19</v>
@@ -1506,69 +1506,69 @@
         <v>0.311</v>
       </c>
       <c r="AE8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.261</v>
+        <v>0.32</v>
       </c>
       <c r="AH8" t="n">
         <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="AK8" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="AL8" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.306</v>
+        <v>0.316</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>776:08</t>
+          <t>831:35</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>471.76</v>
+        <v>506.84</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.444</v>
+        <v>0.458</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.519</v>
+        <v>0.527</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.829</v>
+        <v>0.844</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.201</v>
+        <v>0.199</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.334</v>
+        <v>0.321</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.779</v>
+        <v>1.752</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.282</v>
+        <v>0.281</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.212</v>
+        <v>0.207</v>
       </c>
     </row>
     <row r="9">
@@ -1718,16 +1718,16 @@
         <v>0.3</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.186</v>
+        <v>0.185</v>
       </c>
       <c r="AW9" t="n">
         <v>0.105</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.159</v>
+        <v>0.158</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="10">
@@ -1877,16 +1877,16 @@
         <v>1.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.337</v>
+        <v>0.335</v>
       </c>
       <c r="AW10" t="n">
         <v>0.008</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.105</v>
+        <v>0.104</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="11">
@@ -1896,153 +1896,153 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C11" t="n">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="D11" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E11" t="n">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="F11" t="n">
+        <v>48</v>
+      </c>
+      <c r="G11" t="n">
+        <v>130</v>
+      </c>
+      <c r="H11" t="n">
+        <v>68</v>
+      </c>
+      <c r="I11" t="n">
+        <v>77</v>
+      </c>
+      <c r="J11" t="n">
+        <v>40</v>
+      </c>
+      <c r="K11" t="n">
         <v>47</v>
       </c>
-      <c r="G11" t="n">
-        <v>121</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="L11" t="n">
+        <v>24</v>
+      </c>
+      <c r="M11" t="n">
+        <v>15</v>
+      </c>
+      <c r="N11" t="n">
+        <v>7</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>33</v>
+      </c>
+      <c r="R11" t="n">
+        <v>90</v>
+      </c>
+      <c r="S11" t="n">
         <v>61</v>
       </c>
-      <c r="I11" t="n">
-        <v>69</v>
-      </c>
-      <c r="J11" t="n">
-        <v>37</v>
-      </c>
-      <c r="K11" t="n">
-        <v>45</v>
-      </c>
-      <c r="L11" t="n">
-        <v>21</v>
-      </c>
-      <c r="M11" t="n">
-        <v>13</v>
-      </c>
-      <c r="N11" t="n">
-        <v>6</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>29</v>
-      </c>
-      <c r="R11" t="n">
-        <v>84</v>
-      </c>
-      <c r="S11" t="n">
-        <v>55</v>
-      </c>
       <c r="T11" t="n">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="U11" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="V11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="W11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="X11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Y11" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="Z11" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="AB11" t="n">
         <v>10</v>
       </c>
       <c r="AC11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.333</v>
+        <v>0.312</v>
       </c>
       <c r="AE11" t="n">
         <v>12</v>
       </c>
       <c r="AF11" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.324</v>
+        <v>0.293</v>
       </c>
       <c r="AH11" t="n">
         <v>15</v>
       </c>
       <c r="AI11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.429</v>
+        <v>0.417</v>
       </c>
       <c r="AK11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AL11" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.372</v>
+        <v>0.351</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>678:29</t>
+          <t>723:41</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>274.36</v>
+        <v>301.88</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.509</v>
+        <v>0.489</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.571</v>
+        <v>0.554</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.021</v>
+        <v>0.987</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.106</v>
+        <v>0.109</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.284</v>
+        <v>0.289</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.276</v>
+        <v>1.212</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.187</v>
+        <v>0.192</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.036</v>
+        <v>0.039</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.075</v>
+        <v>0.073</v>
       </c>
       <c r="AY11" t="n">
         <v>0.045</v>
@@ -2055,22 +2055,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H12" t="n">
         <v>31</v>
@@ -2079,16 +2079,16 @@
         <v>42</v>
       </c>
       <c r="J12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N12" t="n">
         <v>6</v>
@@ -2097,25 +2097,25 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R12" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="S12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="T12" t="n">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="U12" t="n">
         <v>11</v>
       </c>
       <c r="V12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="W12" t="n">
         <v>8</v>
@@ -2124,31 +2124,31 @@
         <v>6</v>
       </c>
       <c r="Y12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.737</v>
+        <v>0.741</v>
       </c>
       <c r="AB12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AC12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.611</v>
       </c>
       <c r="AE12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.538</v>
+        <v>0.571</v>
       </c>
       <c r="AH12" t="n">
         <v>1</v>
@@ -2160,51 +2160,51 @@
         <v>0.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AL12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.522</v>
+        <v>0.517</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>408:24</t>
+          <t>438:51</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>129.48</v>
+        <v>140.48</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.674</v>
+        <v>0.696</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.709</v>
+        <v>0.723</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.958</v>
+        <v>1.004</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.324</v>
+        <v>0.306</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.449</v>
+        <v>0.392</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.024</v>
+        <v>2.14</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.147</v>
+        <v>0.148</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.048</v>
+        <v>0.05</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.146</v>
+        <v>0.148</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.097</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="13">
@@ -2354,7 +2354,7 @@
         <v>2</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.331</v>
+        <v>0.329</v>
       </c>
       <c r="AW13" t="n">
         <v>0.141</v>
@@ -2373,156 +2373,156 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D14" t="n">
+        <v>46</v>
+      </c>
+      <c r="E14" t="n">
+        <v>86</v>
+      </c>
+      <c r="F14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G14" t="n">
+        <v>48</v>
+      </c>
+      <c r="H14" t="n">
         <v>40</v>
       </c>
-      <c r="E14" t="n">
-        <v>77</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="I14" t="n">
+        <v>52</v>
+      </c>
+      <c r="J14" t="n">
+        <v>54</v>
+      </c>
+      <c r="K14" t="n">
+        <v>38</v>
+      </c>
+      <c r="L14" t="n">
+        <v>15</v>
+      </c>
+      <c r="M14" t="n">
+        <v>9</v>
+      </c>
+      <c r="N14" t="n">
+        <v>13</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>39</v>
+      </c>
+      <c r="R14" t="n">
+        <v>36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>54</v>
+      </c>
+      <c r="T14" t="n">
+        <v>220</v>
+      </c>
+      <c r="U14" t="n">
+        <v>25</v>
+      </c>
+      <c r="V14" t="n">
+        <v>31</v>
+      </c>
+      <c r="W14" t="n">
+        <v>22</v>
+      </c>
+      <c r="X14" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>79</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>37</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AK14" t="n">
         <v>18</v>
       </c>
-      <c r="G14" t="n">
-        <v>45</v>
-      </c>
-      <c r="H14" t="n">
-        <v>29</v>
-      </c>
-      <c r="I14" t="n">
-        <v>40</v>
-      </c>
-      <c r="J14" t="n">
-        <v>50</v>
-      </c>
-      <c r="K14" t="n">
-        <v>36</v>
-      </c>
-      <c r="L14" t="n">
-        <v>12</v>
-      </c>
-      <c r="M14" t="n">
-        <v>7</v>
-      </c>
-      <c r="N14" t="n">
-        <v>11</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>32</v>
-      </c>
-      <c r="R14" t="n">
-        <v>31</v>
-      </c>
-      <c r="S14" t="n">
-        <v>45</v>
-      </c>
-      <c r="T14" t="n">
-        <v>186</v>
-      </c>
-      <c r="U14" t="n">
-        <v>21</v>
-      </c>
-      <c r="V14" t="n">
-        <v>23</v>
-      </c>
-      <c r="W14" t="n">
-        <v>18</v>
-      </c>
-      <c r="X14" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>45</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>35</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0.457</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0.471</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>17</v>
-      </c>
       <c r="AL14" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.436</v>
+        <v>0.439</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>298:17</t>
+          <t>344:05</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>171.6</v>
+        <v>195.88</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.549</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.584</v>
+        <v>0.612</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.186</v>
+        <v>0.199</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.238</v>
+        <v>0.299</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.562</v>
+        <v>1.385</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.266</v>
+        <v>0.263</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.047</v>
+        <v>0.051</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.136</v>
+        <v>0.124</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.058</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="15">
@@ -2532,22 +2532,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C15" t="n">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="D15" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E15" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G15" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H15" t="n">
         <v>36</v>
@@ -2559,37 +2559,37 @@
         <v>28</v>
       </c>
       <c r="K15" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="L15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R15" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="S15" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="T15" t="n">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="U15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="V15" t="n">
         <v>31</v>
@@ -2601,13 +2601,13 @@
         <v>9</v>
       </c>
       <c r="Y15" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Z15" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.773</v>
+        <v>0.779</v>
       </c>
       <c r="AB15" t="n">
         <v>12</v>
@@ -2619,69 +2619,69 @@
         <v>0.522</v>
       </c>
       <c r="AE15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.733</v>
+        <v>0.706</v>
       </c>
       <c r="AH15" t="n">
         <v>11</v>
       </c>
       <c r="AI15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.289</v>
+        <v>0.282</v>
       </c>
       <c r="AK15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL15" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.313</v>
+        <v>0.324</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>562:46</t>
+          <t>589:40</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>216.36</v>
+        <v>226.36</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.534</v>
+        <v>0.541</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.574</v>
+        <v>0.578</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.026</v>
+        <v>1.034</v>
       </c>
       <c r="AS15" t="n">
         <v>0.106</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.207</v>
+        <v>0.197</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.217</v>
+        <v>1.167</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.178</v>
+        <v>0.177</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
       <c r="AX15" t="n">
         <v>0.144</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="16">
@@ -2691,22 +2691,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F16" t="n">
         <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H16" t="n">
         <v>18</v>
@@ -2718,7 +2718,7 @@
         <v>17</v>
       </c>
       <c r="K16" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L16" t="n">
         <v>15</v>
@@ -2739,7 +2739,7 @@
         <v>11</v>
       </c>
       <c r="R16" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2748,7 +2748,7 @@
         <v>84</v>
       </c>
       <c r="U16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V16" t="n">
         <v>8</v>
@@ -2760,13 +2760,13 @@
         <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.625</v>
+        <v>0.636</v>
       </c>
       <c r="AB16" t="n">
         <v>4</v>
@@ -2790,10 +2790,10 @@
         <v>5</v>
       </c>
       <c r="AI16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.227</v>
+        <v>0.208</v>
       </c>
       <c r="AK16" t="n">
         <v>3</v>
@@ -2806,41 +2806,41 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>380:28</t>
+          <t>385:27</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>82.68000000000001</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="AP16" t="n">
         <v>0.323</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.405</v>
+        <v>0.402</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.701</v>
+        <v>0.7</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.133</v>
+        <v>0.128</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.29</v>
+        <v>0.277</v>
       </c>
       <c r="AU16" t="n">
         <v>1.545</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.101</v>
+        <v>0.103</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="AX16" t="n">
         <v>0.148</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="17">
@@ -2850,16 +2850,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="D17" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E17" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F17" t="n">
         <v>3</v>
@@ -2868,22 +2868,22 @@
         <v>10</v>
       </c>
       <c r="H17" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
+        <v>34</v>
+      </c>
+      <c r="L17" t="n">
         <v>29</v>
       </c>
-      <c r="L17" t="n">
-        <v>27</v>
-      </c>
       <c r="M17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N17" t="n">
         <v>14</v>
@@ -2898,52 +2898,52 @@
         <v>23</v>
       </c>
       <c r="R17" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="S17" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="T17" t="n">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="U17" t="n">
+        <v>11</v>
+      </c>
+      <c r="V17" t="n">
+        <v>29</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>68</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC17" t="n">
         <v>10</v>
       </c>
-      <c r="V17" t="n">
-        <v>22</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>47</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>59</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0.797</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>8</v>
-      </c>
       <c r="AD17" t="n">
-        <v>0.125</v>
+        <v>0.2</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
       </c>
       <c r="AF17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.091</v>
+        <v>0.083</v>
       </c>
       <c r="AH17" t="n">
         <v>2</v>
@@ -2965,41 +2965,41 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>297:30</t>
+          <t>331:17</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>99.8</v>
+        <v>109</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.596</v>
+        <v>0.593</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.612</v>
+        <v>0.616</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.972</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.23</v>
+        <v>0.211</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.191</v>
+        <v>0.227</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.522</v>
+        <v>0.609</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.155</v>
+        <v>0.152</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.106</v>
+        <v>0.102</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.11</v>
+        <v>0.115</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="18">
@@ -3149,16 +3149,16 @@
         <v>1</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.187</v>
+        <v>0.186</v>
       </c>
       <c r="AW18" t="n">
         <v>0.068</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.109</v>
+        <v>0.108</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="19">
@@ -3168,156 +3168,156 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C19" t="n">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E19" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F19" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G19" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="H19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I19" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J19" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K19" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="L19" t="n">
+        <v>33</v>
+      </c>
+      <c r="M19" t="n">
+        <v>21</v>
+      </c>
+      <c r="N19" t="n">
+        <v>7</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>24</v>
+      </c>
+      <c r="R19" t="n">
+        <v>51</v>
+      </c>
+      <c r="S19" t="n">
+        <v>38</v>
+      </c>
+      <c r="T19" t="n">
+        <v>194</v>
+      </c>
+      <c r="U19" t="n">
+        <v>27</v>
+      </c>
+      <c r="V19" t="n">
         <v>29</v>
       </c>
-      <c r="M19" t="n">
-        <v>18</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>19</v>
-      </c>
-      <c r="R19" t="n">
-        <v>48</v>
-      </c>
-      <c r="S19" t="n">
-        <v>35</v>
-      </c>
-      <c r="T19" t="n">
-        <v>174</v>
-      </c>
-      <c r="U19" t="n">
-        <v>24</v>
-      </c>
-      <c r="V19" t="n">
-        <v>26</v>
-      </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z19" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.8</v>
+        <v>0.783</v>
       </c>
       <c r="AB19" t="n">
         <v>12</v>
       </c>
       <c r="AC19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.48</v>
+        <v>0.444</v>
       </c>
       <c r="AE19" t="n">
         <v>8</v>
       </c>
       <c r="AF19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.267</v>
+        <v>0.258</v>
       </c>
       <c r="AH19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AI19" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.368</v>
+        <v>0.455</v>
       </c>
       <c r="AK19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.286</v>
+        <v>0.278</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>527:29</t>
+          <t>576:59</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>216.24</v>
+        <v>236.12</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.438</v>
+        <v>0.442</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.497</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.906</v>
+        <v>0.894</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.102</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.232</v>
+        <v>0.22</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.895</v>
+        <v>0.875</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.19</v>
+        <v>0.189</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.064</v>
+        <v>0.067</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.13</v>
+        <v>0.132</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="20">
@@ -3327,40 +3327,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C20" t="n">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="D20" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E20" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="F20" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G20" t="n">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="H20" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="I20" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="J20" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K20" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="L20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N20" t="n">
         <v>10</v>
@@ -3369,25 +3369,25 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q20" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R20" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="S20" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="T20" t="n">
-        <v>308</v>
+        <v>354</v>
       </c>
       <c r="U20" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="V20" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="W20" t="n">
         <v>15</v>
@@ -3396,13 +3396,13 @@
         <v>9</v>
       </c>
       <c r="Y20" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="Z20" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.844</v>
+        <v>0.86</v>
       </c>
       <c r="AB20" t="n">
         <v>12</v>
@@ -3414,69 +3414,69 @@
         <v>0.375</v>
       </c>
       <c r="AE20" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AF20" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.304</v>
+        <v>0.346</v>
       </c>
       <c r="AH20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.6</v>
+        <v>0.615</v>
       </c>
       <c r="AK20" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="AL20" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.434</v>
+        <v>0.452</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>643:24</t>
+          <t>694:40</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>309.36</v>
+        <v>335.32</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.555</v>
+        <v>0.579</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.602</v>
+        <v>0.626</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.102</v>
+        <v>1.148</v>
       </c>
       <c r="AS20" t="n">
         <v>0.08400000000000001</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.237</v>
+        <v>0.253</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.385</v>
+        <v>1.321</v>
       </c>
       <c r="AV20" t="n">
         <v>0.223</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.045</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="21">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C21" t="n">
         <v>63</v>
@@ -3495,7 +3495,7 @@
         <v>23</v>
       </c>
       <c r="E21" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -3510,37 +3510,37 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K21" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L21" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M21" t="n">
         <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R21" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="S21" t="n">
         <v>19</v>
       </c>
       <c r="T21" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="U21" t="n">
         <v>12</v>
@@ -3567,10 +3567,10 @@
         <v>8</v>
       </c>
       <c r="AC21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3601,41 +3601,41 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>229:10</t>
+          <t>243:26</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>52.56</v>
+        <v>54.56</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.657</v>
+        <v>0.639</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.199</v>
+        <v>1.155</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.133</v>
+        <v>0.147</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.486</v>
+        <v>0.472</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.143</v>
+        <v>1.25</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.106</v>
+        <v>0.103</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.122</v>
+        <v>0.124</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.182</v>
+        <v>0.184</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="22">
@@ -3645,37 +3645,37 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C22" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="D22" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E22" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G22" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="H22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I22" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
         <v>7</v>
       </c>
       <c r="K22" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="L22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M22" t="n">
         <v>17</v>
@@ -3693,34 +3693,34 @@
         <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="S22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T22" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="U22" t="n">
         <v>24</v>
       </c>
       <c r="V22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W22" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="X22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z22" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.769</v>
+        <v>0.762</v>
       </c>
       <c r="AB22" t="n">
         <v>6</v>
@@ -3735,48 +3735,48 @@
         <v>9</v>
       </c>
       <c r="AF22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.6</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AH22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI22" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.226</v>
+        <v>0.216</v>
       </c>
       <c r="AK22" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AL22" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AM22" t="n">
         <v>0.484</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>630:35</t>
+          <t>662:12</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>200.24</v>
+        <v>211.12</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.632</v>
+        <v>0.619</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.641</v>
+        <v>0.628</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.154</v>
+        <v>1.137</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="AT22" t="n">
         <v>0.08799999999999999</v>
@@ -3788,10 +3788,10 @@
         <v>0.147</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.116</v>
+        <v>0.122</v>
       </c>
       <c r="AY22" t="n">
         <v>0.008</v>
@@ -3804,16 +3804,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C23" t="n">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="D23" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E23" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -3822,49 +3822,49 @@
         <v>4</v>
       </c>
       <c r="H23" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I23" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="J23" t="n">
         <v>23</v>
       </c>
       <c r="K23" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="L23" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N23" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="Q23" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="R23" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="S23" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="T23" t="n">
-        <v>475</v>
+        <v>496</v>
       </c>
       <c r="U23" t="n">
         <v>41</v>
       </c>
       <c r="V23" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="W23" t="n">
         <v>13</v>
@@ -3873,31 +3873,31 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="Z23" t="n">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.836</v>
+        <v>0.841</v>
       </c>
       <c r="AB23" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AC23" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.569</v>
       </c>
       <c r="AE23" t="n">
         <v>7</v>
       </c>
       <c r="AF23" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.269</v>
+        <v>0.233</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
@@ -3919,41 +3919,41 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>610:20</t>
+          <t>648:12</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>320.72</v>
+        <v>336.48</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.672</v>
+        <v>0.669</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.731</v>
+        <v>0.728</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.188</v>
+        <v>1.18</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.187</v>
+        <v>0.19</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.552</v>
       </c>
       <c r="AU23" t="n">
-        <v>0.383</v>
+        <v>0.359</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.243</v>
+        <v>0.239</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.103</v>
+        <v>0.106</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.166</v>
+        <v>0.168</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.029</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="24">
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
         <v>63</v>
       </c>
       <c r="L24" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -4005,13 +4005,13 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -4122,150 +4122,150 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C25" t="n">
-        <v>2765</v>
+        <v>2976</v>
       </c>
       <c r="D25" t="n">
-        <v>580</v>
+        <v>626</v>
       </c>
       <c r="E25" t="n">
-        <v>1103</v>
+        <v>1178</v>
       </c>
       <c r="F25" t="n">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="G25" t="n">
-        <v>917</v>
+        <v>984</v>
       </c>
       <c r="H25" t="n">
-        <v>603</v>
+        <v>644</v>
       </c>
       <c r="I25" t="n">
-        <v>758</v>
+        <v>807</v>
       </c>
       <c r="J25" t="n">
-        <v>523</v>
+        <v>554</v>
       </c>
       <c r="K25" t="n">
-        <v>767</v>
+        <v>822</v>
       </c>
       <c r="L25" t="n">
-        <v>337</v>
+        <v>368</v>
       </c>
       <c r="M25" t="n">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="N25" t="n">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>453</v>
+        <v>486</v>
       </c>
       <c r="Q25" t="n">
-        <v>431</v>
+        <v>462</v>
       </c>
       <c r="R25" t="n">
-        <v>747</v>
+        <v>796</v>
       </c>
       <c r="S25" t="n">
-        <v>721</v>
+        <v>771</v>
       </c>
       <c r="T25" t="n">
-        <v>2995</v>
+        <v>3241</v>
       </c>
       <c r="U25" t="n">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="V25" t="n">
-        <v>348</v>
+        <v>389</v>
       </c>
       <c r="W25" t="n">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="X25" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="Y25" t="n">
-        <v>926</v>
+        <v>994</v>
       </c>
       <c r="Z25" t="n">
-        <v>1199</v>
+        <v>1280</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.772</v>
+        <v>0.777</v>
       </c>
       <c r="AB25" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="AC25" t="n">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.416</v>
+        <v>0.417</v>
       </c>
       <c r="AE25" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="AF25" t="n">
-        <v>282</v>
+        <v>312</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.351</v>
+        <v>0.359</v>
       </c>
       <c r="AH25" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="AI25" t="n">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.346</v>
+        <v>0.343</v>
       </c>
       <c r="AK25" t="n">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="AL25" t="n">
-        <v>726</v>
+        <v>774</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.369</v>
+        <v>0.372</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>6500:00</t>
+          <t>6925:00</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>2806.52</v>
+        <v>3003.08</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.535</v>
+        <v>0.539</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.587</v>
+        <v>0.591</v>
       </c>
       <c r="AR25" t="n">
-        <v>0.985</v>
+        <v>0.991</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.161</v>
+        <v>0.162</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.299</v>
+        <v>0.298</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.155</v>
+        <v>1.14</v>
       </c>
       <c r="AV25" t="n">
         <v>0.2</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.06</v>
+        <v>0.062</v>
       </c>
       <c r="AX25" t="n">
         <v>0.133</v>
@@ -4281,144 +4281,144 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C26" t="n">
-        <v>2981</v>
+        <v>3169</v>
       </c>
       <c r="D26" t="n">
-        <v>674</v>
+        <v>718</v>
       </c>
       <c r="E26" t="n">
-        <v>1144</v>
+        <v>1227</v>
       </c>
       <c r="F26" t="n">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="G26" t="n">
-        <v>999</v>
+        <v>1054</v>
       </c>
       <c r="H26" t="n">
-        <v>604</v>
+        <v>647</v>
       </c>
       <c r="I26" t="n">
-        <v>808</v>
+        <v>865</v>
       </c>
       <c r="J26" t="n">
-        <v>615</v>
+        <v>651</v>
       </c>
       <c r="K26" t="n">
-        <v>780</v>
+        <v>821</v>
       </c>
       <c r="L26" t="n">
-        <v>389</v>
+        <v>415</v>
       </c>
       <c r="M26" t="n">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="N26" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="Q26" t="n">
-        <v>367</v>
+        <v>394</v>
       </c>
       <c r="R26" t="n">
-        <v>721</v>
+        <v>770</v>
       </c>
       <c r="S26" t="n">
-        <v>747</v>
+        <v>795</v>
       </c>
       <c r="T26" t="n">
-        <v>3473</v>
+        <v>3677</v>
       </c>
       <c r="U26" t="n">
-        <v>368</v>
+        <v>403</v>
       </c>
       <c r="V26" t="n">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="W26" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="X26" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>1067</v>
       </c>
       <c r="Z26" t="n">
-        <v>1319</v>
+        <v>1406</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="AB26" t="n">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="AC26" t="n">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.497</v>
+        <v>0.496</v>
       </c>
       <c r="AE26" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="AF26" t="n">
-        <v>259</v>
+        <v>287</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.355</v>
+        <v>0.348</v>
       </c>
       <c r="AH26" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI26" t="n">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.371</v>
+        <v>0.374</v>
       </c>
       <c r="AK26" t="n">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="AL26" t="n">
-        <v>759</v>
+        <v>800</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.335</v>
+        <v>0.334</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>6500:00</t>
+          <t>6925:00</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>2889.52</v>
+        <v>3079.6</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.555</v>
+        <v>0.553</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.597</v>
+        <v>0.595</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.032</v>
+        <v>1.029</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.135</v>
+        <v>0.136</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.282</v>
+        <v>0.284</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.573</v>
+        <v>1.557</v>
       </c>
       <c r="AV26" t="n">
         <v>0.2</v>
@@ -4427,7 +4427,7 @@
         <v>0.067</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.14</v>
+        <v>0.138</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
@@ -4637,13 +4637,13 @@
         <v>0.3</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.186</v>
+        <v>0.185</v>
       </c>
       <c r="AW28" t="n">
         <v>0.105</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.159</v>
+        <v>0.158</v>
       </c>
       <c r="AY28" t="n">
         <v>0.011</v>
@@ -4656,156 +4656,156 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C29" t="n">
-        <v>13.033</v>
+        <v>13.375</v>
       </c>
       <c r="D29" t="n">
-        <v>2.233</v>
+        <v>2.375</v>
       </c>
       <c r="E29" t="n">
-        <v>5.2</v>
+        <v>5.219</v>
       </c>
       <c r="F29" t="n">
-        <v>1.667</v>
+        <v>1.719</v>
       </c>
       <c r="G29" t="n">
-        <v>5.467</v>
+        <v>5.594</v>
       </c>
       <c r="H29" t="n">
-        <v>3.567</v>
+        <v>3.469</v>
       </c>
       <c r="I29" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="J29" t="n">
-        <v>5.633</v>
+        <v>5.531</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>2.094</v>
       </c>
       <c r="L29" t="n">
-        <v>0.367</v>
+        <v>0.375</v>
       </c>
       <c r="M29" t="n">
-        <v>1.233</v>
+        <v>1.219</v>
       </c>
       <c r="N29" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.531</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.167</v>
+        <v>3.156</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.167</v>
+        <v>3.156</v>
       </c>
       <c r="R29" t="n">
-        <v>2</v>
+        <v>1.906</v>
       </c>
       <c r="S29" t="n">
-        <v>4.633</v>
+        <v>4.656</v>
       </c>
       <c r="T29" t="n">
-        <v>444</v>
+        <v>487</v>
       </c>
       <c r="U29" t="n">
-        <v>1.7</v>
+        <v>1.688</v>
       </c>
       <c r="V29" t="n">
-        <v>0.8</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="W29" t="n">
-        <v>1.2</v>
+        <v>1.188</v>
       </c>
       <c r="X29" t="n">
-        <v>0.733</v>
+        <v>0.719</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.967</v>
+        <v>5</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.7</v>
+        <v>6.781</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.741</v>
+        <v>0.737</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.633</v>
+        <v>0.594</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.033</v>
+        <v>1.906</v>
       </c>
       <c r="AD29" t="n">
         <v>0.311</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.767</v>
+        <v>0.781</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.261</v>
+        <v>0.32</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.133</v>
+        <v>0.25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.633</v>
+        <v>1.688</v>
       </c>
       <c r="AL29" t="n">
-        <v>5.333</v>
+        <v>5.344</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.306</v>
+        <v>0.316</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>25:52</t>
+          <t>25:59</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>15.725</v>
+        <v>15.839</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.444</v>
+        <v>0.458</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.519</v>
+        <v>0.527</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.829</v>
+        <v>0.844</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.201</v>
+        <v>0.199</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.334</v>
+        <v>0.321</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.779</v>
+        <v>1.752</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.282</v>
+        <v>0.281</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.228</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="30">
@@ -4955,16 +4955,16 @@
         <v>1.2</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.337</v>
+        <v>0.335</v>
       </c>
       <c r="AW30" t="n">
         <v>0.008</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.105</v>
+        <v>0.104</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -4974,153 +4974,153 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>8.75</v>
+        <v>8.765000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>1.219</v>
+        <v>1.265</v>
       </c>
       <c r="E31" t="n">
-        <v>2.938</v>
+        <v>3.088</v>
       </c>
       <c r="F31" t="n">
-        <v>1.469</v>
+        <v>1.412</v>
       </c>
       <c r="G31" t="n">
-        <v>3.781</v>
+        <v>3.824</v>
       </c>
       <c r="H31" t="n">
-        <v>1.906</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>2.156</v>
+        <v>2.265</v>
       </c>
       <c r="J31" t="n">
-        <v>1.156</v>
+        <v>1.176</v>
       </c>
       <c r="K31" t="n">
-        <v>1.406</v>
+        <v>1.382</v>
       </c>
       <c r="L31" t="n">
-        <v>0.656</v>
+        <v>0.706</v>
       </c>
       <c r="M31" t="n">
-        <v>0.406</v>
+        <v>0.441</v>
       </c>
       <c r="N31" t="n">
-        <v>0.188</v>
+        <v>0.206</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.906</v>
+        <v>0.971</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.906</v>
+        <v>0.971</v>
       </c>
       <c r="R31" t="n">
-        <v>2.625</v>
+        <v>2.647</v>
       </c>
       <c r="S31" t="n">
-        <v>1.719</v>
+        <v>1.794</v>
       </c>
       <c r="T31" t="n">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="U31" t="n">
-        <v>1.188</v>
+        <v>1.206</v>
       </c>
       <c r="V31" t="n">
-        <v>0.781</v>
+        <v>0.794</v>
       </c>
       <c r="W31" t="n">
-        <v>0.906</v>
+        <v>0.912</v>
       </c>
       <c r="X31" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.588</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.438</v>
+        <v>2.618</v>
       </c>
       <c r="Z31" t="n">
-        <v>3</v>
+        <v>3.206</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="AB31" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="AD31" t="n">
         <v>0.312</v>
       </c>
-      <c r="AC31" t="n">
-        <v>0.9379999999999999</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0.333</v>
-      </c>
       <c r="AE31" t="n">
-        <v>0.375</v>
+        <v>0.353</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.156</v>
+        <v>1.206</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.324</v>
+        <v>0.293</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.469</v>
+        <v>0.441</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.094</v>
+        <v>1.059</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.429</v>
+        <v>0.417</v>
       </c>
       <c r="AK31" t="n">
-        <v>1</v>
+        <v>0.971</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.688</v>
+        <v>2.765</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.372</v>
+        <v>0.351</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>8.574</v>
+        <v>8.879</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.509</v>
+        <v>0.489</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.571</v>
+        <v>0.554</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.021</v>
+        <v>0.987</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.106</v>
+        <v>0.109</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.284</v>
+        <v>0.289</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.276</v>
+        <v>1.212</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.187</v>
+        <v>0.192</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.036</v>
+        <v>0.039</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.075</v>
+        <v>0.073</v>
       </c>
       <c r="AY31" t="n">
         <v>0.045</v>
@@ -5133,156 +5133,156 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C32" t="n">
-        <v>4.769</v>
+        <v>5.036</v>
       </c>
       <c r="D32" t="n">
-        <v>1.038</v>
+        <v>1.107</v>
       </c>
       <c r="E32" t="n">
-        <v>1.692</v>
+        <v>1.714</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="G32" t="n">
-        <v>0.962</v>
+        <v>1.107</v>
       </c>
       <c r="H32" t="n">
-        <v>1.192</v>
+        <v>1.107</v>
       </c>
       <c r="I32" t="n">
-        <v>1.615</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
-        <v>3.269</v>
+        <v>3.286</v>
       </c>
       <c r="K32" t="n">
-        <v>2.038</v>
+        <v>2.071</v>
       </c>
       <c r="L32" t="n">
-        <v>0.654</v>
+        <v>0.679</v>
       </c>
       <c r="M32" t="n">
-        <v>0.538</v>
+        <v>0.536</v>
       </c>
       <c r="N32" t="n">
-        <v>0.231</v>
+        <v>0.214</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.615</v>
+        <v>1.536</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.615</v>
+        <v>1.536</v>
       </c>
       <c r="R32" t="n">
-        <v>1.731</v>
+        <v>1.821</v>
       </c>
       <c r="S32" t="n">
-        <v>1.462</v>
+        <v>1.429</v>
       </c>
       <c r="T32" t="n">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="U32" t="n">
-        <v>0.423</v>
+        <v>0.393</v>
       </c>
       <c r="V32" t="n">
-        <v>1.192</v>
+        <v>1.179</v>
       </c>
       <c r="W32" t="n">
-        <v>0.308</v>
+        <v>0.286</v>
       </c>
       <c r="X32" t="n">
-        <v>0.231</v>
+        <v>0.214</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.615</v>
+        <v>1.536</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.192</v>
+        <v>2.071</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.737</v>
+        <v>0.741</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.346</v>
+        <v>0.393</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.615</v>
+        <v>0.643</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.611</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.269</v>
+        <v>0.286</v>
       </c>
       <c r="AF32" t="n">
         <v>0.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.538</v>
+        <v>0.571</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.077</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AJ32" t="n">
         <v>0.5</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.462</v>
+        <v>0.536</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.885</v>
+        <v>1.036</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.522</v>
+        <v>0.517</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>4.98</v>
+        <v>5.017</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.674</v>
+        <v>0.696</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.709</v>
+        <v>0.723</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.958</v>
+        <v>1.004</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.324</v>
+        <v>0.306</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.449</v>
+        <v>0.392</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.024</v>
+        <v>2.14</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.147</v>
+        <v>0.148</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.048</v>
+        <v>0.05</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.146</v>
+        <v>0.148</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.121</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="33">
@@ -5432,7 +5432,7 @@
         <v>2</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.331</v>
+        <v>0.329</v>
       </c>
       <c r="AW33" t="n">
         <v>0.141</v>
@@ -5451,156 +5451,156 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C34" t="n">
-        <v>13.583</v>
+        <v>13.714</v>
       </c>
       <c r="D34" t="n">
-        <v>3.333</v>
+        <v>3.286</v>
       </c>
       <c r="E34" t="n">
-        <v>6.417</v>
+        <v>6.143</v>
       </c>
       <c r="F34" t="n">
-        <v>1.5</v>
+        <v>1.429</v>
       </c>
       <c r="G34" t="n">
-        <v>3.75</v>
+        <v>3.429</v>
       </c>
       <c r="H34" t="n">
-        <v>2.417</v>
+        <v>2.857</v>
       </c>
       <c r="I34" t="n">
-        <v>3.333</v>
+        <v>3.714</v>
       </c>
       <c r="J34" t="n">
-        <v>4.167</v>
+        <v>3.857</v>
       </c>
       <c r="K34" t="n">
-        <v>3</v>
+        <v>2.714</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>1.071</v>
       </c>
       <c r="M34" t="n">
-        <v>0.583</v>
+        <v>0.643</v>
       </c>
       <c r="N34" t="n">
-        <v>0.917</v>
+        <v>0.929</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.667</v>
+        <v>2.786</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.667</v>
+        <v>2.786</v>
       </c>
       <c r="R34" t="n">
-        <v>2.583</v>
+        <v>2.571</v>
       </c>
       <c r="S34" t="n">
-        <v>3.75</v>
+        <v>3.857</v>
       </c>
       <c r="T34" t="n">
-        <v>186</v>
+        <v>220</v>
       </c>
       <c r="U34" t="n">
-        <v>1.75</v>
+        <v>1.786</v>
       </c>
       <c r="V34" t="n">
-        <v>1.917</v>
+        <v>2.214</v>
       </c>
       <c r="W34" t="n">
-        <v>1.5</v>
+        <v>1.571</v>
       </c>
       <c r="X34" t="n">
-        <v>0.917</v>
+        <v>1.071</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.75</v>
+        <v>4.143</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.417</v>
+        <v>5.643</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.734</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.333</v>
+        <v>1.214</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.917</v>
+        <v>2.643</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.457</v>
+        <v>0.459</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.667</v>
+        <v>0.786</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.417</v>
+        <v>1.571</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.471</v>
+        <v>0.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.083</v>
+        <v>0.143</v>
       </c>
       <c r="AI34" t="n">
         <v>0.5</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.167</v>
+        <v>0.286</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.417</v>
+        <v>1.286</v>
       </c>
       <c r="AL34" t="n">
-        <v>3.25</v>
+        <v>2.929</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.436</v>
+        <v>0.439</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>24:51</t>
+          <t>24:34</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>14.3</v>
+        <v>13.991</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.549</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.584</v>
+        <v>0.612</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.186</v>
+        <v>0.199</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.238</v>
+        <v>0.299</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.563</v>
+        <v>1.385</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.266</v>
+        <v>0.263</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.047</v>
+        <v>0.051</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.136</v>
+        <v>0.124</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.176</v>
+        <v>0.159</v>
       </c>
     </row>
     <row r="35">
@@ -5610,40 +5610,40 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C35" t="n">
-        <v>8.538</v>
+        <v>8.356999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>1.731</v>
+        <v>1.714</v>
       </c>
       <c r="E35" t="n">
-        <v>2.654</v>
+        <v>2.607</v>
       </c>
       <c r="F35" t="n">
-        <v>1.231</v>
+        <v>1.214</v>
       </c>
       <c r="G35" t="n">
-        <v>4.038</v>
+        <v>3.929</v>
       </c>
       <c r="H35" t="n">
-        <v>1.385</v>
+        <v>1.286</v>
       </c>
       <c r="I35" t="n">
-        <v>1.692</v>
+        <v>1.571</v>
       </c>
       <c r="J35" t="n">
-        <v>1.077</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>2.769</v>
+        <v>2.714</v>
       </c>
       <c r="L35" t="n">
-        <v>0.731</v>
+        <v>0.714</v>
       </c>
       <c r="M35" t="n">
-        <v>0.846</v>
+        <v>0.821</v>
       </c>
       <c r="N35" t="n">
         <v>0.5</v>
@@ -5652,114 +5652,114 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.885</v>
+        <v>0.857</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.885</v>
+        <v>0.857</v>
       </c>
       <c r="R35" t="n">
-        <v>2.462</v>
+        <v>2.357</v>
       </c>
       <c r="S35" t="n">
-        <v>1.231</v>
+        <v>1.25</v>
       </c>
       <c r="T35" t="n">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="U35" t="n">
-        <v>1.462</v>
+        <v>1.429</v>
       </c>
       <c r="V35" t="n">
-        <v>1.192</v>
+        <v>1.107</v>
       </c>
       <c r="W35" t="n">
-        <v>0.615</v>
+        <v>0.571</v>
       </c>
       <c r="X35" t="n">
-        <v>0.346</v>
+        <v>0.321</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.231</v>
+        <v>2.143</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.885</v>
+        <v>2.75</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.773</v>
+        <v>0.779</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.462</v>
+        <v>0.429</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.885</v>
+        <v>0.821</v>
       </c>
       <c r="AD35" t="n">
         <v>0.522</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.423</v>
+        <v>0.429</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.577</v>
+        <v>0.607</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.733</v>
+        <v>0.706</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.423</v>
+        <v>0.393</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.462</v>
+        <v>1.393</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.289</v>
+        <v>0.282</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.821</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.577</v>
+        <v>2.536</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.313</v>
+        <v>0.324</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>21:38</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>8.321999999999999</v>
+        <v>8.084</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.534</v>
+        <v>0.541</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.574</v>
+        <v>0.578</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.026</v>
+        <v>1.034</v>
       </c>
       <c r="AS35" t="n">
         <v>0.106</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.207</v>
+        <v>0.197</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.217</v>
+        <v>1.167</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.178</v>
+        <v>0.177</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
       <c r="AX35" t="n">
         <v>0.144</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.042</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="36">
@@ -5769,156 +5769,156 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C36" t="n">
-        <v>1.812</v>
+        <v>1.765</v>
       </c>
       <c r="D36" t="n">
-        <v>0.25</v>
+        <v>0.265</v>
       </c>
       <c r="E36" t="n">
-        <v>0.906</v>
+        <v>0.882</v>
       </c>
       <c r="F36" t="n">
-        <v>0.25</v>
+        <v>0.235</v>
       </c>
       <c r="G36" t="n">
-        <v>1.031</v>
+        <v>1.029</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.529</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.647</v>
       </c>
       <c r="J36" t="n">
-        <v>0.531</v>
+        <v>0.5</v>
       </c>
       <c r="K36" t="n">
-        <v>1.562</v>
+        <v>1.5</v>
       </c>
       <c r="L36" t="n">
-        <v>0.469</v>
+        <v>0.441</v>
       </c>
       <c r="M36" t="n">
-        <v>0.625</v>
+        <v>0.588</v>
       </c>
       <c r="N36" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.344</v>
+        <v>0.324</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.344</v>
+        <v>0.324</v>
       </c>
       <c r="R36" t="n">
-        <v>1.344</v>
+        <v>1.294</v>
       </c>
       <c r="S36" t="n">
-        <v>0.781</v>
+        <v>0.735</v>
       </c>
       <c r="T36" t="n">
         <v>84</v>
       </c>
       <c r="U36" t="n">
-        <v>0.25</v>
+        <v>0.294</v>
       </c>
       <c r="V36" t="n">
-        <v>0.25</v>
+        <v>0.235</v>
       </c>
       <c r="W36" t="n">
-        <v>0.312</v>
+        <v>0.294</v>
       </c>
       <c r="X36" t="n">
-        <v>0.156</v>
+        <v>0.147</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.625</v>
+        <v>0.618</v>
       </c>
       <c r="Z36" t="n">
-        <v>1</v>
+        <v>0.971</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.625</v>
+        <v>0.636</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.125</v>
+        <v>0.118</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.375</v>
+        <v>0.353</v>
       </c>
       <c r="AD36" t="n">
         <v>0.333</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="AG36" t="n">
         <v>0.286</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.156</v>
+        <v>0.147</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.706</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.227</v>
+        <v>0.208</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.344</v>
+        <v>0.324</v>
       </c>
       <c r="AM36" t="n">
         <v>0.273</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>2.584</v>
+        <v>2.52</v>
       </c>
       <c r="AP36" t="n">
         <v>0.323</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.405</v>
+        <v>0.402</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.701</v>
+        <v>0.7</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.133</v>
+        <v>0.128</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.29</v>
+        <v>0.277</v>
       </c>
       <c r="AU36" t="n">
         <v>1.545</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.101</v>
+        <v>0.103</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="AX36" t="n">
         <v>0.148</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="37">
@@ -5928,156 +5928,156 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C37" t="n">
-        <v>4.273</v>
+        <v>4.417</v>
       </c>
       <c r="D37" t="n">
-        <v>1.636</v>
+        <v>1.667</v>
       </c>
       <c r="E37" t="n">
-        <v>2.636</v>
+        <v>2.708</v>
       </c>
       <c r="F37" t="n">
-        <v>0.136</v>
+        <v>0.125</v>
       </c>
       <c r="G37" t="n">
-        <v>0.455</v>
+        <v>0.417</v>
       </c>
       <c r="H37" t="n">
-        <v>0.591</v>
+        <v>0.708</v>
       </c>
       <c r="I37" t="n">
-        <v>0.909</v>
+        <v>1.042</v>
       </c>
       <c r="J37" t="n">
-        <v>0.545</v>
+        <v>0.583</v>
       </c>
       <c r="K37" t="n">
-        <v>1.318</v>
+        <v>1.417</v>
       </c>
       <c r="L37" t="n">
-        <v>1.227</v>
+        <v>1.208</v>
       </c>
       <c r="M37" t="n">
-        <v>0.318</v>
+        <v>0.458</v>
       </c>
       <c r="N37" t="n">
-        <v>0.636</v>
+        <v>0.583</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.045</v>
+        <v>0.958</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.045</v>
+        <v>0.958</v>
       </c>
       <c r="R37" t="n">
-        <v>2</v>
+        <v>1.875</v>
       </c>
       <c r="S37" t="n">
-        <v>1.045</v>
+        <v>1.125</v>
       </c>
       <c r="T37" t="n">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="U37" t="n">
-        <v>0.455</v>
+        <v>0.458</v>
       </c>
       <c r="V37" t="n">
-        <v>1</v>
+        <v>1.208</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.136</v>
+        <v>2.25</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.682</v>
+        <v>2.833</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.797</v>
+        <v>0.794</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.045</v>
+        <v>0.083</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.364</v>
+        <v>0.417</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.125</v>
+        <v>0.2</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.045</v>
+        <v>0.042</v>
       </c>
       <c r="AF37" t="n">
         <v>0.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.091</v>
+        <v>0.083</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.091</v>
+        <v>0.083</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.136</v>
+        <v>0.125</v>
       </c>
       <c r="AJ37" t="n">
         <v>0.667</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.045</v>
+        <v>0.042</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.318</v>
+        <v>0.292</v>
       </c>
       <c r="AM37" t="n">
         <v>0.143</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>4.536</v>
+        <v>4.542</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.596</v>
+        <v>0.593</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.612</v>
+        <v>0.616</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.972</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.23</v>
+        <v>0.211</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.191</v>
+        <v>0.227</v>
       </c>
       <c r="AU37" t="n">
-        <v>0.522</v>
+        <v>0.609</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.155</v>
+        <v>0.152</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.106</v>
+        <v>0.102</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.11</v>
+        <v>0.115</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="38">
@@ -6227,13 +6227,13 @@
         <v>1</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.187</v>
+        <v>0.186</v>
       </c>
       <c r="AW38" t="n">
         <v>0.068</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.109</v>
+        <v>0.108</v>
       </c>
       <c r="AY38" t="n">
         <v>0.028</v>
@@ -6246,156 +6246,156 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C39" t="n">
-        <v>6.533</v>
+        <v>6.594</v>
       </c>
       <c r="D39" t="n">
-        <v>1.033</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>2.467</v>
+        <v>2.469</v>
       </c>
       <c r="F39" t="n">
-        <v>1.033</v>
+        <v>1.094</v>
       </c>
       <c r="G39" t="n">
-        <v>3.433</v>
+        <v>3.5</v>
       </c>
       <c r="H39" t="n">
-        <v>1.367</v>
+        <v>1.312</v>
       </c>
       <c r="I39" t="n">
-        <v>1.533</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.656</v>
       </c>
       <c r="K39" t="n">
-        <v>2.033</v>
+        <v>2.125</v>
       </c>
       <c r="L39" t="n">
-        <v>0.967</v>
+        <v>1.031</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6</v>
+        <v>0.656</v>
       </c>
       <c r="N39" t="n">
-        <v>0.167</v>
+        <v>0.219</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.633</v>
+        <v>0.75</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.633</v>
+        <v>0.75</v>
       </c>
       <c r="R39" t="n">
-        <v>1.6</v>
+        <v>1.594</v>
       </c>
       <c r="S39" t="n">
-        <v>1.167</v>
+        <v>1.188</v>
       </c>
       <c r="T39" t="n">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="U39" t="n">
-        <v>0.8</v>
+        <v>0.844</v>
       </c>
       <c r="V39" t="n">
-        <v>0.867</v>
+        <v>0.906</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.733</v>
+        <v>1.688</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.167</v>
+        <v>2.156</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.8</v>
+        <v>0.783</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.833</v>
+        <v>0.844</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.48</v>
+        <v>0.444</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.267</v>
+        <v>0.25</v>
       </c>
       <c r="AF39" t="n">
-        <v>1</v>
+        <v>0.969</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.267</v>
+        <v>0.258</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.233</v>
+        <v>0.312</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.633</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.368</v>
+        <v>0.455</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.8</v>
+        <v>0.781</v>
       </c>
       <c r="AL39" t="n">
-        <v>2.8</v>
+        <v>2.812</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.286</v>
+        <v>0.278</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>7.208</v>
+        <v>7.379</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.438</v>
+        <v>0.442</v>
       </c>
       <c r="AQ39" t="n">
         <v>0.497</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.906</v>
+        <v>0.894</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.102</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.232</v>
+        <v>0.22</v>
       </c>
       <c r="AU39" t="n">
-        <v>0.895</v>
+        <v>0.875</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.19</v>
+        <v>0.189</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.064</v>
+        <v>0.067</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.13</v>
+        <v>0.132</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.021</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="40">
@@ -6405,156 +6405,156 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C40" t="n">
-        <v>11.367</v>
+        <v>12.031</v>
       </c>
       <c r="D40" t="n">
-        <v>1.633</v>
+        <v>1.75</v>
       </c>
       <c r="E40" t="n">
-        <v>4.067</v>
+        <v>4.125</v>
       </c>
       <c r="F40" t="n">
-        <v>2.033</v>
+        <v>2.125</v>
       </c>
       <c r="G40" t="n">
-        <v>4.367</v>
+        <v>4.406</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>2.156</v>
       </c>
       <c r="I40" t="n">
-        <v>2.3</v>
+        <v>2.438</v>
       </c>
       <c r="J40" t="n">
-        <v>1.2</v>
+        <v>1.156</v>
       </c>
       <c r="K40" t="n">
-        <v>1.633</v>
+        <v>1.688</v>
       </c>
       <c r="L40" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>0.467</v>
+        <v>0.5</v>
       </c>
       <c r="N40" t="n">
-        <v>0.333</v>
+        <v>0.312</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.867</v>
+        <v>0.875</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.867</v>
+        <v>0.875</v>
       </c>
       <c r="R40" t="n">
-        <v>1.533</v>
+        <v>1.625</v>
       </c>
       <c r="S40" t="n">
-        <v>2.167</v>
+        <v>2.25</v>
       </c>
       <c r="T40" t="n">
-        <v>308</v>
+        <v>354</v>
       </c>
       <c r="U40" t="n">
-        <v>0.633</v>
+        <v>0.75</v>
       </c>
       <c r="V40" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2.688</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AC40" t="n">
         <v>1</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.533</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.067</v>
       </c>
       <c r="AD40" t="n">
         <v>0.375</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.7</v>
+        <v>0.844</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.3</v>
+        <v>2.438</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.304</v>
+        <v>0.346</v>
       </c>
       <c r="AH40" t="n">
         <v>0.5</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.833</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.6</v>
+        <v>0.615</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.533</v>
+        <v>1.625</v>
       </c>
       <c r="AL40" t="n">
-        <v>3.533</v>
+        <v>3.594</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.434</v>
+        <v>0.452</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>10.312</v>
+        <v>10.479</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.555</v>
+        <v>0.579</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.602</v>
+        <v>0.626</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.102</v>
+        <v>1.148</v>
       </c>
       <c r="AS40" t="n">
         <v>0.08400000000000001</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.237</v>
+        <v>0.253</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.385</v>
+        <v>1.321</v>
       </c>
       <c r="AV40" t="n">
         <v>0.223</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.048</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="41">
@@ -6564,16 +6564,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C41" t="n">
-        <v>1.969</v>
+        <v>1.853</v>
       </c>
       <c r="D41" t="n">
-        <v>0.719</v>
+        <v>0.676</v>
       </c>
       <c r="E41" t="n">
-        <v>1.094</v>
+        <v>1.059</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -6582,79 +6582,79 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.531</v>
+        <v>0.5</v>
       </c>
       <c r="I41" t="n">
-        <v>0.75</v>
+        <v>0.706</v>
       </c>
       <c r="J41" t="n">
-        <v>0.25</v>
+        <v>0.294</v>
       </c>
       <c r="K41" t="n">
-        <v>1.156</v>
+        <v>1.176</v>
       </c>
       <c r="L41" t="n">
-        <v>0.75</v>
+        <v>0.765</v>
       </c>
       <c r="M41" t="n">
-        <v>0.125</v>
+        <v>0.118</v>
       </c>
       <c r="N41" t="n">
-        <v>0.125</v>
+        <v>0.176</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.219</v>
+        <v>0.235</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.219</v>
+        <v>0.235</v>
       </c>
       <c r="R41" t="n">
-        <v>1.125</v>
+        <v>1.147</v>
       </c>
       <c r="S41" t="n">
-        <v>0.594</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="T41" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="U41" t="n">
-        <v>0.375</v>
+        <v>0.353</v>
       </c>
       <c r="V41" t="n">
-        <v>0.531</v>
+        <v>0.5</v>
       </c>
       <c r="W41" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="X41" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="Y41" t="n">
-        <v>1</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.312</v>
+        <v>1.235</v>
       </c>
       <c r="AA41" t="n">
         <v>0.762</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.25</v>
+        <v>0.235</v>
       </c>
       <c r="AC41" t="n">
         <v>0.5</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -6683,37 +6683,37 @@
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>1.643</v>
+        <v>1.605</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.657</v>
+        <v>0.639</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.199</v>
+        <v>1.155</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.133</v>
+        <v>0.147</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.486</v>
+        <v>0.472</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.143</v>
+        <v>1.25</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.106</v>
+        <v>0.103</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.122</v>
+        <v>0.124</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.182</v>
+        <v>0.184</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="42">
@@ -6723,138 +6723,138 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C42" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="D42" t="n">
-        <v>1.071</v>
+        <v>1.033</v>
       </c>
       <c r="E42" t="n">
-        <v>1.679</v>
+        <v>1.633</v>
       </c>
       <c r="F42" t="n">
-        <v>1.857</v>
+        <v>1.8</v>
       </c>
       <c r="G42" t="n">
-        <v>4.429</v>
+        <v>4.4</v>
       </c>
       <c r="H42" t="n">
-        <v>0.536</v>
+        <v>0.533</v>
       </c>
       <c r="I42" t="n">
-        <v>0.75</v>
+        <v>0.767</v>
       </c>
       <c r="J42" t="n">
-        <v>0.25</v>
+        <v>0.233</v>
       </c>
       <c r="K42" t="n">
-        <v>2.321</v>
+        <v>2.4</v>
       </c>
       <c r="L42" t="n">
-        <v>0.571</v>
+        <v>0.6</v>
       </c>
       <c r="M42" t="n">
-        <v>0.607</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>0.536</v>
+        <v>0.5</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="R42" t="n">
-        <v>2.571</v>
+        <v>2.633</v>
       </c>
       <c r="S42" t="n">
-        <v>0.75</v>
+        <v>0.733</v>
       </c>
       <c r="T42" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="U42" t="n">
-        <v>0.857</v>
+        <v>0.8</v>
       </c>
       <c r="V42" t="n">
-        <v>0.571</v>
+        <v>0.6</v>
       </c>
       <c r="W42" t="n">
-        <v>0.714</v>
+        <v>0.8</v>
       </c>
       <c r="X42" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.071</v>
+        <v>1.067</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.393</v>
+        <v>1.4</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.769</v>
+        <v>0.762</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.214</v>
+        <v>0.2</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.5</v>
+        <v>0.467</v>
       </c>
       <c r="AD42" t="n">
         <v>0.429</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.321</v>
+        <v>0.3</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.536</v>
+        <v>0.533</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.6</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.25</v>
+        <v>0.267</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.107</v>
+        <v>1.233</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.226</v>
+        <v>0.216</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.607</v>
+        <v>1.533</v>
       </c>
       <c r="AL42" t="n">
-        <v>3.321</v>
+        <v>3.167</v>
       </c>
       <c r="AM42" t="n">
         <v>0.484</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:04</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>7.151</v>
+        <v>7.037</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.632</v>
+        <v>0.619</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.641</v>
+        <v>0.628</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.154</v>
+        <v>1.137</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="AT42" t="n">
         <v>0.08799999999999999</v>
@@ -6866,13 +6866,13 @@
         <v>0.147</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.116</v>
+        <v>0.122</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -6882,100 +6882,100 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C43" t="n">
-        <v>11.906</v>
+        <v>11.676</v>
       </c>
       <c r="D43" t="n">
-        <v>4.156</v>
+        <v>4.088</v>
       </c>
       <c r="E43" t="n">
-        <v>6.125</v>
+        <v>6.059</v>
       </c>
       <c r="F43" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="G43" t="n">
-        <v>0.125</v>
+        <v>0.118</v>
       </c>
       <c r="H43" t="n">
-        <v>3.5</v>
+        <v>3.412</v>
       </c>
       <c r="I43" t="n">
-        <v>4.312</v>
+        <v>4.176</v>
       </c>
       <c r="J43" t="n">
-        <v>0.719</v>
+        <v>0.676</v>
       </c>
       <c r="K43" t="n">
-        <v>2.812</v>
+        <v>2.853</v>
       </c>
       <c r="L43" t="n">
-        <v>1.688</v>
+        <v>1.735</v>
       </c>
       <c r="M43" t="n">
-        <v>0.281</v>
+        <v>0.294</v>
       </c>
       <c r="N43" t="n">
-        <v>0.844</v>
+        <v>0.853</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.875</v>
+        <v>1.882</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.875</v>
+        <v>1.882</v>
       </c>
       <c r="R43" t="n">
-        <v>3.188</v>
+        <v>3.206</v>
       </c>
       <c r="S43" t="n">
-        <v>4.531</v>
+        <v>4.412</v>
       </c>
       <c r="T43" t="n">
-        <v>475</v>
+        <v>496</v>
       </c>
       <c r="U43" t="n">
-        <v>1.281</v>
+        <v>1.206</v>
       </c>
       <c r="V43" t="n">
-        <v>1.781</v>
+        <v>1.794</v>
       </c>
       <c r="W43" t="n">
-        <v>0.406</v>
+        <v>0.382</v>
       </c>
       <c r="X43" t="n">
-        <v>0.25</v>
+        <v>0.235</v>
       </c>
       <c r="Y43" t="n">
-        <v>6.219</v>
+        <v>6.088</v>
       </c>
       <c r="Z43" t="n">
-        <v>7.438</v>
+        <v>7.235</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.836</v>
+        <v>0.841</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.219</v>
+        <v>1.206</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.188</v>
+        <v>2.118</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.569</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.882</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.269</v>
+        <v>0.233</v>
       </c>
       <c r="AH43" t="n">
         <v>0</v>
@@ -6987,51 +6987,51 @@
         <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="AL43" t="n">
-        <v>0.125</v>
+        <v>0.118</v>
       </c>
       <c r="AM43" t="n">
         <v>0.25</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>10.022</v>
+        <v>9.896000000000001</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.672</v>
+        <v>0.669</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.731</v>
+        <v>0.728</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.188</v>
+        <v>1.18</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.187</v>
+        <v>0.19</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.552</v>
       </c>
       <c r="AU43" t="n">
-        <v>0.383</v>
+        <v>0.359</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.243</v>
+        <v>0.239</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.103</v>
+        <v>0.106</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.166</v>
+        <v>0.168</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.029</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="44">
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -7068,10 +7068,10 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>1.969</v>
+        <v>1.853</v>
       </c>
       <c r="L44" t="n">
-        <v>1.406</v>
+        <v>1.471</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -7083,13 +7083,13 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.706</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.031</v>
+        <v>0.059</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -7200,150 +7200,150 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C45" t="n">
-        <v>86.40600000000001</v>
+        <v>87.529</v>
       </c>
       <c r="D45" t="n">
-        <v>18.125</v>
+        <v>18.412</v>
       </c>
       <c r="E45" t="n">
-        <v>34.469</v>
+        <v>34.647</v>
       </c>
       <c r="F45" t="n">
-        <v>10.438</v>
+        <v>10.588</v>
       </c>
       <c r="G45" t="n">
-        <v>28.656</v>
+        <v>28.941</v>
       </c>
       <c r="H45" t="n">
-        <v>18.844</v>
+        <v>18.941</v>
       </c>
       <c r="I45" t="n">
-        <v>23.688</v>
+        <v>23.735</v>
       </c>
       <c r="J45" t="n">
-        <v>16.344</v>
+        <v>16.294</v>
       </c>
       <c r="K45" t="n">
-        <v>23.969</v>
+        <v>24.176</v>
       </c>
       <c r="L45" t="n">
-        <v>10.531</v>
+        <v>10.824</v>
       </c>
       <c r="M45" t="n">
-        <v>6.281</v>
+        <v>6.441</v>
       </c>
       <c r="N45" t="n">
-        <v>4.438</v>
+        <v>4.471</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>14.156</v>
+        <v>14.294</v>
       </c>
       <c r="Q45" t="n">
-        <v>13.469</v>
+        <v>13.588</v>
       </c>
       <c r="R45" t="n">
-        <v>23.344</v>
+        <v>23.412</v>
       </c>
       <c r="S45" t="n">
-        <v>22.531</v>
+        <v>22.676</v>
       </c>
       <c r="T45" t="n">
-        <v>2995</v>
+        <v>3241</v>
       </c>
       <c r="U45" t="n">
-        <v>10.062</v>
+        <v>10.147</v>
       </c>
       <c r="V45" t="n">
-        <v>10.875</v>
+        <v>11.441</v>
       </c>
       <c r="W45" t="n">
-        <v>5.719</v>
+        <v>5.853</v>
       </c>
       <c r="X45" t="n">
-        <v>3.438</v>
+        <v>3.588</v>
       </c>
       <c r="Y45" t="n">
-        <v>28.938</v>
+        <v>29.235</v>
       </c>
       <c r="Z45" t="n">
-        <v>37.469</v>
+        <v>37.647</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.772</v>
+        <v>0.777</v>
       </c>
       <c r="AB45" t="n">
-        <v>4.938</v>
+        <v>4.824</v>
       </c>
       <c r="AC45" t="n">
-        <v>11.875</v>
+        <v>11.559</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.416</v>
+        <v>0.417</v>
       </c>
       <c r="AE45" t="n">
-        <v>3.094</v>
+        <v>3.294</v>
       </c>
       <c r="AF45" t="n">
-        <v>8.811999999999999</v>
+        <v>9.176</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.351</v>
+        <v>0.359</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.062</v>
+        <v>2.118</v>
       </c>
       <c r="AI45" t="n">
-        <v>5.969</v>
+        <v>6.176</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.346</v>
+        <v>0.343</v>
       </c>
       <c r="AK45" t="n">
-        <v>8.375</v>
+        <v>8.471</v>
       </c>
       <c r="AL45" t="n">
-        <v>22.688</v>
+        <v>22.765</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.369</v>
+        <v>0.372</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>203:07</t>
+          <t>203:40</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>87.70399999999999</v>
+        <v>88.32599999999999</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.535</v>
+        <v>0.539</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.587</v>
+        <v>0.591</v>
       </c>
       <c r="AR45" t="n">
-        <v>0.985</v>
+        <v>0.991</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.161</v>
+        <v>0.162</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.299</v>
+        <v>0.298</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.155</v>
+        <v>1.14</v>
       </c>
       <c r="AV45" t="n">
         <v>0.2</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.06</v>
+        <v>0.062</v>
       </c>
       <c r="AX45" t="n">
         <v>0.133</v>
@@ -7359,153 +7359,153 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C46" t="n">
-        <v>93.15600000000001</v>
+        <v>93.206</v>
       </c>
       <c r="D46" t="n">
-        <v>21.062</v>
+        <v>21.118</v>
       </c>
       <c r="E46" t="n">
-        <v>35.75</v>
+        <v>36.088</v>
       </c>
       <c r="F46" t="n">
-        <v>10.719</v>
+        <v>10.647</v>
       </c>
       <c r="G46" t="n">
-        <v>31.219</v>
+        <v>31</v>
       </c>
       <c r="H46" t="n">
-        <v>18.875</v>
+        <v>19.029</v>
       </c>
       <c r="I46" t="n">
-        <v>25.25</v>
+        <v>25.441</v>
       </c>
       <c r="J46" t="n">
-        <v>19.219</v>
+        <v>19.147</v>
       </c>
       <c r="K46" t="n">
-        <v>24.375</v>
+        <v>24.147</v>
       </c>
       <c r="L46" t="n">
-        <v>12.156</v>
+        <v>12.206</v>
       </c>
       <c r="M46" t="n">
-        <v>8.031000000000001</v>
+        <v>8.206</v>
       </c>
       <c r="N46" t="n">
-        <v>4.562</v>
+        <v>4.529</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>12.219</v>
+        <v>12.294</v>
       </c>
       <c r="Q46" t="n">
-        <v>11.469</v>
+        <v>11.588</v>
       </c>
       <c r="R46" t="n">
-        <v>22.531</v>
+        <v>22.647</v>
       </c>
       <c r="S46" t="n">
-        <v>23.344</v>
+        <v>23.382</v>
       </c>
       <c r="T46" t="n">
-        <v>3473</v>
+        <v>3677</v>
       </c>
       <c r="U46" t="n">
-        <v>11.5</v>
+        <v>11.853</v>
       </c>
       <c r="V46" t="n">
-        <v>12.438</v>
+        <v>12.559</v>
       </c>
       <c r="W46" t="n">
-        <v>7</v>
+        <v>6.971</v>
       </c>
       <c r="X46" t="n">
-        <v>3.969</v>
+        <v>3.971</v>
       </c>
       <c r="Y46" t="n">
-        <v>31.25</v>
+        <v>31.382</v>
       </c>
       <c r="Z46" t="n">
-        <v>41.219</v>
+        <v>41.353</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="AB46" t="n">
-        <v>5.812</v>
+        <v>5.824</v>
       </c>
       <c r="AC46" t="n">
-        <v>11.688</v>
+        <v>11.735</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.497</v>
+        <v>0.496</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.875</v>
+        <v>2.941</v>
       </c>
       <c r="AF46" t="n">
-        <v>8.093999999999999</v>
+        <v>8.441000000000001</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.355</v>
+        <v>0.348</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.781</v>
+        <v>2.794</v>
       </c>
       <c r="AI46" t="n">
-        <v>7.5</v>
+        <v>7.471</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.371</v>
+        <v>0.374</v>
       </c>
       <c r="AK46" t="n">
-        <v>7.938</v>
+        <v>7.853</v>
       </c>
       <c r="AL46" t="n">
-        <v>23.719</v>
+        <v>23.529</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.335</v>
+        <v>0.334</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>203:07</t>
+          <t>203:40</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>90.298</v>
+        <v>90.57599999999999</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.555</v>
+        <v>0.553</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.597</v>
+        <v>0.595</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.032</v>
+        <v>1.029</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.135</v>
+        <v>0.136</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.282</v>
+        <v>0.284</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.573</v>
+        <v>1.557</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.206</v>
+        <v>0.205</v>
       </c>
       <c r="AW46" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.135</v>
+        <v>0.133</v>
       </c>
       <c r="AY46" t="n">
         <v>0</v>
